--- a/config/sources.xlsx
+++ b/config/sources.xlsx
@@ -2030,12 +2030,12 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourcesCyberwatch12" displayName="SourcesCyberwatch12" ref="A1:S79" headerRowCount="1" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourcesCyberwatch12" displayName="SourcesCyberwatch12" ref="A1:T110" headerRowCount="1" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="A1:S79"/>
   <sortState ref="A2:Q41">
     <sortCondition ref="A1:A41"/>
   </sortState>
-  <tableColumns count="19">
+  <tableColumns count="20">
     <tableColumn id="6" name="Zone géographique concernée" dataDxfId="54"/>
     <tableColumn id="1" name="Nom de la Source" dataDxfId="53"/>
     <tableColumn id="14" name="Préconisateur" dataDxfId="52"/>
@@ -2055,6 +2055,7 @@
     <tableColumn id="13" name="Notes / Commentaires" dataDxfId="38"/>
     <tableColumn id="18" name="URL pages actualités (une par ligne)"/>
     <tableColumn id="19" name="Vérification (23/09/2026)"/>
+    <tableColumn id="20" name="Filtrage (vide = tout garder ; « pertinence » = source très volumineuse, ne garder que pertinence moyenne ou élevée)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4655,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S79"/>
+  <dimension ref="A1:T110"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.1796875" customWidth="1" min="1" max="1"/>
@@ -4677,6 +4678,7 @@
     <col width="74.453125" customWidth="1" min="17" max="17"/>
     <col width="55" customWidth="1" min="18" max="18"/>
     <col width="70" customWidth="1" min="19" max="19"/>
+    <col width="28" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="39" customHeight="1">
@@ -4773,6 +4775,11 @@
       <c r="S1" s="75" t="inlineStr">
         <is>
           <t>Vérification (23/09/2026)</t>
+        </is>
+      </c>
+      <c r="T1" s="75" t="inlineStr">
+        <is>
+          <t>Filtrage (vide = tout garder ; « pertinence » = source très volumineuse, ne garder que pertinence moyenne ou élevée)</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5119,7 @@
       <c r="R6" s="131" t="n"/>
       <c r="S6" s="131" t="inlineStr">
         <is>
-          <t>23/09/2026 : flux RSS lisible mais les articles renvoient tous une erreur 403 → passé en Inactif. Ses communiqués sont repris par news.belgium.be.</t>
+          <t>Vérif. 24/09/2026 : flux RSS lu (16/09/2026, CRA et NIS2) ; articles 403 pour un robot, lisibles dans un navigateur</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5218,11 @@
           <t>https://www.ccn-cert.cni.es/</t>
         </is>
       </c>
-      <c r="F8" s="134" t="n"/>
+      <c r="F8" s="134" t="inlineStr">
+        <is>
+          <t>https://www.ccn-cert.cni.es/es/seguridad-al-dia/actualidad-ccn.html?format=feed&amp;type=rss</t>
+        </is>
+      </c>
       <c r="G8" s="135" t="n"/>
       <c r="H8" s="109" t="inlineStr">
         <is>
@@ -5226,7 +5237,7 @@
       </c>
       <c r="K8" s="115" t="inlineStr">
         <is>
-          <t>Partiel - à revérifier</t>
+          <t>Actif - à confirmer</t>
         </is>
       </c>
       <c r="L8" s="116" t="inlineStr">
@@ -5247,10 +5258,14 @@
           <t>Correction (18/09/2026, 2e passe) : je n'ai PAS trouvé d'article daté 2025/2026 avec une URL exploitable. La page d'accueil affiche un exemple ancien (2016, sans URL), et les 2 sous-pages alertes/actualités testées renvoient toutes les deux une erreur 403. Statut revu à la baisse : accessible mais flux d'actus non confirmé.</t>
         </is>
       </c>
-      <c r="R8" s="131" t="n"/>
+      <c r="R8" s="131" t="inlineStr">
+        <is>
+          <t>https://www.ccn-cert.cni.es/es/seguridad-al-dia/actualidad-ccn.html</t>
+        </is>
+      </c>
       <c r="S8" s="131" t="inlineStr">
         <is>
-          <t>Toujours bloqué (erreur 403) le 23/09/2026 : source à remplacer ou à consulter manuellement.</t>
+          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
         </is>
       </c>
     </row>
@@ -5380,10 +5395,7 @@
       </c>
       <c r="S10" s="131" t="inlineStr">
         <is>
-          <t>Pages repérées sur le site le 23/09/2026 (actualités, publications, certification &amp; standards). (recherche du 23/09/2026)
-Retiré le 23/09/2026 :
-- https://www.enisa.europa.eu/topics/product-security-and-certification (page thématique sans dates)
-- https://www.enisa.europa.eu/topics/certification-and-standards (page thématique sans dates)</t>
+          <t>Vérif. 24/09/2026 : page lue le 24/09/2026 (aucun flux RSS trouvé : /rss.xml = 404, aucun lien RSS sur les pages) : dernier élément du 22/09/2026 ; article ouvert : https://www.enisa.europa.eu/news/the-cra-single-reporting-platform-is-launched (11/09/2026).</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6000,11 @@
           <t>https://health.ec.europa.eu/medical-devices-sector/new-regulations/guidance-mdcg-endorsed-documents-and-other-guidance_en</t>
         </is>
       </c>
-      <c r="F20" s="136" t="n"/>
+      <c r="F20" s="136" t="inlineStr">
+        <is>
+          <t>https://health.ec.europa.eu/node/2/rss_en</t>
+        </is>
+      </c>
       <c r="G20" s="137" t="n"/>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -6026,16 +6042,13 @@
       </c>
       <c r="R20" s="141" t="inlineStr">
         <is>
-          <t>https://health.ec.europa.eu/medical-devices-sector/new-regulations/guidance-mdcg-endorsed-documents-and-other-guidance_en</t>
+          <t>https://health.ec.europa.eu/medical-devices-sector/new-regulations/guidance-mdcg-endorsed-documents-and-other-guidance_en
+https://health.ec.europa.eu/latest-updates_en</t>
         </is>
       </c>
       <c r="S20" s="131" t="inlineStr">
         <is>
-          <t>Guidances MDCG + dernières mises à jour DG SANTE + pages IVD et nouveaux règlements. (recherche du 23/09/2026)
-Retiré le 23/09/2026 :
-- https://health.ec.europa.eu/latest-updates_en (déplacée vers la nouvelle ligne DG SANTE)
-- https://health.ec.europa.eu/medical-devices-vitro-diagnostics_en (page thématique sans dates)
-- https://health.ec.europa.eu/medical-devices-new-regulations_en (page thématique sans dates)</t>
+          <t>Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 02/07/2026 (le flux semble en retard sur la page, dont le dernier élément est du 18/09/2026 : garder la page en secours) ; article ouvert : https://health.ec.europa.eu/latest-updates/three-new-templates-support-written-input-patients-carers-and-clinicians-joint-clinical-assessments-2026-09-14_en. Couvre EHDS, HTA, organismes notifiés DM/DIV ; volume modéré, beaucoup d'éléments hors cyber.</t>
         </is>
       </c>
     </row>
@@ -6422,7 +6435,11 @@
           <t>https://cyber.gov.gr/</t>
         </is>
       </c>
-      <c r="F26" s="136" t="n"/>
+      <c r="F26" s="136" t="inlineStr">
+        <is>
+          <t>https://cyber.gov.gr/feed/</t>
+        </is>
+      </c>
       <c r="G26" s="137" t="n"/>
       <c r="H26" s="7" t="inlineStr">
         <is>
@@ -6466,10 +6483,7 @@
       </c>
       <c r="S26" s="131" t="inlineStr">
         <is>
-          <t>Communiqués + annonces + législation grecque cyber + page NIS2. (recherche du 23/09/2026)
-Retiré le 23/09/2026 :
-- https://cyber.gov.gr/nomothesia/elliniki-nomothesia-gia-tin-kyvernoasfaleia/ (page de textes sans dates de publication)
-- https://cyber.gov.gr/odigia-nis2/ (page thématique sans dates)</t>
+          <t>Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 21/09/2026 ; article ouvert : https://cyber.gov.gr/cyber-resilience-act-nees-ypochreoseis-anaforas-gia-oloys-toys-kataskeyastes-proionton-me-psifiaka-stoicheia-apo-simera/ (obligations de déclaration du CRA, 11/09/2026)</t>
         </is>
       </c>
     </row>
@@ -6604,15 +6618,13 @@
       </c>
       <c r="R28" s="140" t="inlineStr">
         <is>
-          <t>https://nsm.no/aktuelt/</t>
+          <t>https://nsm.no/aktuelt/
+https://nsm.no/aktuelt</t>
         </is>
       </c>
       <c r="S28" s="131" t="inlineStr">
         <is>
-          <t>Actualités vérifiées (dernière le 15/09/2026) + loi sur la sécurité numérique (NIS) + recommandations. (recherche du 23/09/2026)
-Retiré le 23/09/2026 :
-- https://nsm.no/regelverk-og-hjelp/digitalsikkerhetsloven-og-forskriften/ (page thématique sans dates)
-- https://nsm.no/regelverk-og-hjelp/rad-og-anbefalinger/ (page thématique sans dates)</t>
+          <t>Vérif. 24/09/2026 : page lue le 24/09/2026 : dernier élément du 15/09/2026 (actualités/avis, pas d'alertes techniques ; pas de flux RSS) ; article ouvert : https://nsm.no/aktuelt/tiltak-mot-tjenestenektangrep. Source déjà présente : on ajoute seulement la page d'actualités datées.</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6669,7 @@
       </c>
       <c r="K29" s="29" t="inlineStr">
         <is>
-          <t>Partiel - contenu JS non accessible</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="L29" s="17" t="inlineStr">
@@ -6681,10 +6693,7 @@
       <c r="R29" s="140" t="n"/>
       <c r="S29" s="131" t="inlineStr">
         <is>
-          <t>Flux actualités (contourne le JavaScript) + pages nieuws et publicaties. (recherche du 23/09/2026)
-Retiré le 23/09/2026 :
-- https://www.ncsc.nl/nieuws (liste chargée en JavaScript)
-- https://www.ncsc.nl/publicaties (liste chargée en JavaScript)</t>
+          <t>Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 23/09/2026 ; article ouvert : https://www.ncsc.nl/nieuws/eerste-ict-dienstverleners-gecertificeerd-voor-keurmerk-digitale-basisveiligheid-mkb (contenu complet, donc le problème JS signalé est levé). Attention : le flux mélange /nieuws/ et /alerts/ (vulnérabilités) ; filtrer côté script sur les URL contenant /nieuws/.</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6869,7 @@
       </c>
       <c r="F32" s="136" t="inlineStr">
         <is>
-          <t>https://www.ncsc.gov.uk/api/1/services/v1/news-rss-feed.xml</t>
+          <t>https://www.ncsc.gov.uk/api/1/services/v1/all-rss-feed.xml</t>
         </is>
       </c>
       <c r="G32" s="137" t="inlineStr">
@@ -6905,10 +6914,7 @@
       <c r="R32" s="140" t="n"/>
       <c r="S32" s="131" t="inlineStr">
         <is>
-          <t>Flux News + Guidance + pages actualités et guides. (recherche du 23/09/2026)
-Retiré le 23/09/2026 :
-- https://www.ncsc.gov.uk/section/keep-up-to-date (liste chargée en JavaScript)
-- https://www.ncsc.gov.uk/section/advice-guidance/all-articles (liste chargée en JavaScript)</t>
+          <t>Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 21/09/2026 (mélange news, blogs, guidance — ex. schéma de certification CyAS) ; article ouvert : https://www.ncsc.gov.uk/blogs/cyber-adversary-simulation-cyas-scheme-documents-now-available (17/09/2026). Complète le flux news-only existant</t>
         </is>
       </c>
     </row>
@@ -7799,7 +7805,11 @@
           <t>https://cert.pl</t>
         </is>
       </c>
-      <c r="F47" s="129" t="n"/>
+      <c r="F47" s="129" t="inlineStr">
+        <is>
+          <t>https://cert.pl/en/rss.xml</t>
+        </is>
+      </c>
       <c r="G47" s="130" t="n"/>
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="10" t="n"/>
@@ -7830,9 +7840,7 @@
       </c>
       <c r="S47" s="131" t="inlineStr">
         <is>
-          <t>Page d'accueil (derniers articles) + publications. (recherche du 23/09/2026)
-Retiré le 23/09/2026 :
-- https://cert.pl/publikacje/ (rapports mensuels sans date précise)</t>
+          <t>Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 23/09/2026 (RSS 2.0 ; beaucoup d'avis CVE mais aussi des analyses et des rapports de sujets) ; article ouvert : https://cert.pl/en/posts/2026/09/tollfraud-analysis/</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8160,11 @@
           <t>https://digst.dk</t>
         </is>
       </c>
-      <c r="F53" s="129" t="n"/>
+      <c r="F53" s="129" t="inlineStr">
+        <is>
+          <t>https://digst.dk/nyheder/nyhedsarkiv/?rss=true</t>
+        </is>
+      </c>
       <c r="G53" s="130" t="n"/>
       <c r="H53" s="9" t="n"/>
       <c r="I53" s="10" t="n"/>
@@ -8183,13 +8195,7 @@
       </c>
       <c r="S53" s="131" t="inlineStr">
         <is>
-          <t>Actualités + pages NIS2, AI Act et Data Act de l'autorité danoise. (recherche du 23/09/2026)
-Retiré le 23/09/2026 :
-- https://digst.dk/nyheder/ (page hub sans dates (remplacée par l'archive des actualités))
-- https://digst.dk/tilsyn/nis-2/ (page thématique sans dates)
-- https://digst.dk/tilsyn/ai-forordningen/ (page thématique sans dates)
-- https://digst.dk/tilsyn/dataforordningen/ (page thématique sans dates)
-Ajouté : archive des actualités (datée, dernière le 14/09/2026, dont supervision AI Act).</t>
+          <t>Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 22/09/2026 (RSS 2.0) ; article ouvert (texte lisible, résumé du flux) : https://digst.dk/nyheder/nyhedsarkiv/2026/september/nye-oekonomiske-noegletal-for-telebranchen/ ; page d'archive affiche aussi le 14/09/2026 « Første tilsyn med forbudt AI-praksis er afsluttet »</t>
         </is>
       </c>
     </row>
@@ -8433,8 +8439,16 @@
           <t>https://nki.gov.hu</t>
         </is>
       </c>
-      <c r="F58" s="129" t="n"/>
-      <c r="G58" s="130" t="n"/>
+      <c r="F58" s="129" t="inlineStr">
+        <is>
+          <t>https://nki.gov.hu/feed/hirek/</t>
+        </is>
+      </c>
+      <c r="G58" s="130" t="inlineStr">
+        <is>
+          <t>https://nki.gov.hu/feed/kiadvanyok/</t>
+        </is>
+      </c>
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="10" t="n"/>
       <c r="J58" s="9" t="n"/>
@@ -8466,7 +8480,7 @@
       </c>
       <c r="S58" s="131" t="inlineStr">
         <is>
-          <t>Actualités (vérifiées, septembre 2026) + informations + publications. (recherche du 23/09/2026)</t>
+          <t>Vérif. 24/09/2026 : flux hirek lu le 24/09/2026 : dernier élément du 04/09/2026 (RSS 2.0 ; le flux est en retard, le site affiche des actualités au 24/09/2026) ; article ouvert : https://nki.gov.hu/it-biztonsag/hirek/153-millio-jogositvany-adatai-szivarogtak-ki/. Flux kiadvanyok (publications) listé sur https://nki.gov.hu/intezet/tartalom/rss-csatornak/ mais non ouvert. Ne pas prendre /feed/serulekenysegek ni /feed/riasztasok (alertes).</t>
         </is>
       </c>
     </row>
@@ -9917,6 +9931,1680 @@
       <c r="S79" s="131" t="inlineStr">
         <is>
           <t>Page « Brèves » datée vérifiée (dernière le 03/09/2026) et article ouvert avec succès.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="152" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="B80" s="153" t="inlineStr">
+        <is>
+          <t>gematik (agence nationale de la télématique de santé) – Newsroom</t>
+        </is>
+      </c>
+      <c r="C80" s="154" t="n"/>
+      <c r="D80" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E80" s="155" t="inlineStr">
+        <is>
+          <t>https://www.gematik.de/newsroom</t>
+        </is>
+      </c>
+      <c r="F80" s="142" t="inlineStr">
+        <is>
+          <t>https://www.gematik.de/newsroom/rss.feed</t>
+        </is>
+      </c>
+      <c r="G80" s="128" t="n"/>
+      <c r="H80" s="153" t="n"/>
+      <c r="I80" s="153" t="n"/>
+      <c r="J80" s="156" t="n"/>
+      <c r="K80" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L80" s="157" t="n"/>
+      <c r="M80" s="157" t="n"/>
+      <c r="N80" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O80" s="159" t="n"/>
+      <c r="P80" s="153" t="n"/>
+      <c r="Q80" s="160" t="n"/>
+      <c r="R80" s="131" t="inlineStr">
+        <is>
+          <t>https://www.gematik.de/newsroom</t>
+        </is>
+      </c>
+      <c r="S80" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux lu le 24/09/2026 : dernier élément du 23/09/2026 ; article ouvert : https://www.gematik.de/newsroom/news-detail/3-fragen-an-sebastian-labinski-leiter-cyber-defense-center</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="152" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="B81" s="153" t="inlineStr">
+        <is>
+          <t>Bundesministerium für Gesundheit (BMG) – Pressemitteilungen</t>
+        </is>
+      </c>
+      <c r="C81" s="154" t="n"/>
+      <c r="D81" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E81" s="155" t="inlineStr">
+        <is>
+          <t>https://www.bundesgesundheitsministerium.de/</t>
+        </is>
+      </c>
+      <c r="F81" s="142" t="inlineStr">
+        <is>
+          <t>https://www.bundesgesundheitsministerium.de/pressemitteilungen.xml</t>
+        </is>
+      </c>
+      <c r="G81" s="128" t="n"/>
+      <c r="H81" s="153" t="n"/>
+      <c r="I81" s="153" t="n"/>
+      <c r="J81" s="156" t="n"/>
+      <c r="K81" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L81" s="157" t="n"/>
+      <c r="M81" s="157" t="n"/>
+      <c r="N81" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O81" s="159" t="n"/>
+      <c r="P81" s="153" t="n"/>
+      <c r="Q81" s="160" t="n"/>
+      <c r="R81" s="131" t="inlineStr">
+        <is>
+          <t>https://www.bundesgesundheitsministerium.de/presse/pressemitteilungen.html</t>
+        </is>
+      </c>
+      <c r="S81" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux lu le 24/09/2026 : dernier élément du 04/09/2026 ; article ouvert : https://www.bundesgesundheitsministerium.de/presse/pressemitteilungen/kabinett-beschliesst-gedig-pm-15-07-2026 (loi GeDIG, données et innovation numérique en santé). Autre flux proposé par la page https://www.bundesgesundheitsministerium.de/rss : meldungen.xml (non testé ; l'URL meldungen.rss a expiré)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="152" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="B82" s="153" t="inlineStr">
+        <is>
+          <t>Deutsches Ärzteblatt – Nachrichten</t>
+        </is>
+      </c>
+      <c r="C82" s="154" t="n"/>
+      <c r="D82" s="153" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E82" s="155" t="inlineStr">
+        <is>
+          <t>https://www.aerzteblatt.de/</t>
+        </is>
+      </c>
+      <c r="F82" s="142" t="inlineStr">
+        <is>
+          <t>https://www.aerzteblatt.de/rss/news.asp</t>
+        </is>
+      </c>
+      <c r="G82" s="128" t="n"/>
+      <c r="H82" s="153" t="n"/>
+      <c r="I82" s="153" t="n"/>
+      <c r="J82" s="156" t="n"/>
+      <c r="K82" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L82" s="157" t="n"/>
+      <c r="M82" s="157" t="n"/>
+      <c r="N82" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O82" s="159" t="n"/>
+      <c r="P82" s="153" t="n"/>
+      <c r="Q82" s="160" t="n"/>
+      <c r="R82" s="131" t="n"/>
+      <c r="S82" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe D — flux lu le 24/09/2026 : dernier élément du 23/09/2026 ; article ouvert : https://www.aerzteblatt.de/news/linnemann-zeigt-sich-vor-abgeordneten-entscheidungsfreudig-f6b94bd7-24a9-4d13-82b5-1ff632c61a79. Flux généraliste santé, gros volume : filtrer par mots-clés (Digitalisierung, ePA, Cyber, KRITIS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="152" t="inlineStr">
+        <is>
+          <t>Autriche</t>
+        </is>
+      </c>
+      <c r="B83" s="153" t="inlineStr">
+        <is>
+          <t>Ministère fédéral autrichien du travail, des affaires sociales, de la santé, des soins et de la protection des consommateurs (BMASGPK) – communiqués sur APA-OTS</t>
+        </is>
+      </c>
+      <c r="C83" s="154" t="n"/>
+      <c r="D83" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E83" s="155" t="inlineStr">
+        <is>
+          <t>https://www.sozialministerium.gv.at/</t>
+        </is>
+      </c>
+      <c r="F83" s="142" t="n"/>
+      <c r="G83" s="128" t="n"/>
+      <c r="H83" s="153" t="n"/>
+      <c r="I83" s="153" t="n"/>
+      <c r="J83" s="156" t="n"/>
+      <c r="K83" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L83" s="157" t="n"/>
+      <c r="M83" s="157" t="n"/>
+      <c r="N83" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O83" s="159" t="n"/>
+      <c r="P83" s="153" t="n"/>
+      <c r="Q83" s="160" t="n"/>
+      <c r="R83" s="131" t="inlineStr">
+        <is>
+          <t>https://www.ots.at/pressemappe/46/bundesministerium-fuer-arbeit-soziales-gesundheit-und-konsumentenschutz</t>
+        </is>
+      </c>
+      <c r="S83" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — page lue le 24/09/2026 (le site du ministère renvoie vers ce dossier de presse OTS, aucun flux RSS affiché) : dernier élément du 24/09/2026 ; article ouvert : https://www.ots.at/presseaussendung/OTS_20260917_OTS0006/welttag-der-patientinnensicherheit-hitzeschutz-ist-patientinnensicherheit</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="152" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="B84" s="153" t="inlineStr">
+        <is>
+          <t>AgID – Agenzia per l'Italia Digitale (notizie)</t>
+        </is>
+      </c>
+      <c r="C84" s="154" t="n"/>
+      <c r="D84" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E84" s="155" t="inlineStr">
+        <is>
+          <t>https://www.agid.gov.it/it/notizie</t>
+        </is>
+      </c>
+      <c r="F84" s="142" t="inlineStr">
+        <is>
+          <t>https://www.agid.gov.it/it/rss.xml</t>
+        </is>
+      </c>
+      <c r="G84" s="128" t="n"/>
+      <c r="H84" s="153" t="n"/>
+      <c r="I84" s="153" t="n"/>
+      <c r="J84" s="156" t="n"/>
+      <c r="K84" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L84" s="157" t="n"/>
+      <c r="M84" s="157" t="n"/>
+      <c r="N84" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O84" s="159" t="n"/>
+      <c r="P84" s="153" t="n"/>
+      <c r="Q84" s="160" t="n"/>
+      <c r="R84" s="131" t="inlineStr">
+        <is>
+          <t>https://www.agid.gov.it/it/notizie</t>
+        </is>
+      </c>
+      <c r="S84" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe B — flux lu le 24/09/2026 : dernier élément du 21/09/2026 ; article ouvert : https://www.agid.gov.it/it/notizie/dichiarazione-di-accessibilita-pubblicazione-o-aggiornamento-entro-il-23-settembre</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="152" t="inlineStr">
+        <is>
+          <t>Grèce</t>
+        </is>
+      </c>
+      <c r="B85" s="153" t="inlineStr">
+        <is>
+          <t>Ministère grec de la santé (Υπουργείο Υγείας) – communiqués de presse</t>
+        </is>
+      </c>
+      <c r="C85" s="154" t="n"/>
+      <c r="D85" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E85" s="155" t="inlineStr">
+        <is>
+          <t>https://www.moh.gov.gr/</t>
+        </is>
+      </c>
+      <c r="F85" s="142" t="n"/>
+      <c r="G85" s="128" t="n"/>
+      <c r="H85" s="153" t="n"/>
+      <c r="I85" s="153" t="n"/>
+      <c r="J85" s="156" t="n"/>
+      <c r="K85" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L85" s="157" t="n"/>
+      <c r="M85" s="157" t="n"/>
+      <c r="N85" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O85" s="159" t="n"/>
+      <c r="P85" s="153" t="n"/>
+      <c r="Q85" s="160" t="n"/>
+      <c r="R85" s="131" t="inlineStr">
+        <is>
+          <t>https://www.moh.gov.gr/articles/newspaper/press-releases</t>
+        </is>
+      </c>
+      <c r="S85" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — page lue le 24/09/2026 (« ?format=feed&amp;type=rss » renvoie la page HTML, pas de RSS) : dernier élément du 23/09/2026 ; article ouvert : https://www.moh.gov.gr/articles/ministry/grafeio-typoy/press-releases/14725-synanthsh-toy-ypoyrgoy-ygeias-me-eyrwboyleytes-ths-epitrophs-dhmosias-ygeias-sant-toy-eyrwpaikoy-koinoboylioy</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="152" t="inlineStr">
+        <is>
+          <t>Pays-Bas</t>
+        </is>
+      </c>
+      <c r="B86" s="153" t="inlineStr">
+        <is>
+          <t>Z-CERT (CERT sectoriel de la santé néerlandaise)</t>
+        </is>
+      </c>
+      <c r="C86" s="154" t="n"/>
+      <c r="D86" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E86" s="155" t="inlineStr">
+        <is>
+          <t>https://z-cert.nl/</t>
+        </is>
+      </c>
+      <c r="F86" s="142" t="n"/>
+      <c r="G86" s="128" t="n"/>
+      <c r="H86" s="153" t="n"/>
+      <c r="I86" s="153" t="n"/>
+      <c r="J86" s="156" t="n"/>
+      <c r="K86" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L86" s="157" t="n"/>
+      <c r="M86" s="157" t="n"/>
+      <c r="N86" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O86" s="159" t="n"/>
+      <c r="P86" s="153" t="n"/>
+      <c r="Q86" s="160" t="n"/>
+      <c r="R86" s="131" t="inlineStr">
+        <is>
+          <t>https://z-cert.nl/actueel/nieuws</t>
+        </is>
+      </c>
+      <c r="S86" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe C — page lue le 24/09/2026 (pas de flux RSS : /feed/ = 404) : dernier élément du 23/09/2026 ; article ouvert : https://z-cert.nl/actueel/nieuws/de-cyberbeveiligingswet-is-van-kracht (15/08/2026, entrée en vigueur de la Cyberbeveiligingswet / NIS2 NL). Mélange actus réglementaires et avertissements (phishing, WordPress).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="152" t="inlineStr">
+        <is>
+          <t>Pays-Bas</t>
+        </is>
+      </c>
+      <c r="B87" s="153" t="inlineStr">
+        <is>
+          <t>Nictiz (centre d'expertise santé numérique, normes d'échange, EHDS)</t>
+        </is>
+      </c>
+      <c r="C87" s="154" t="n"/>
+      <c r="D87" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E87" s="155" t="inlineStr">
+        <is>
+          <t>https://www.nictiz.nl/</t>
+        </is>
+      </c>
+      <c r="F87" s="142" t="n"/>
+      <c r="G87" s="128" t="n"/>
+      <c r="H87" s="153" t="n"/>
+      <c r="I87" s="153" t="n"/>
+      <c r="J87" s="156" t="n"/>
+      <c r="K87" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L87" s="157" t="n"/>
+      <c r="M87" s="157" t="n"/>
+      <c r="N87" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O87" s="159" t="n"/>
+      <c r="P87" s="153" t="n"/>
+      <c r="Q87" s="160" t="n"/>
+      <c r="R87" s="131" t="inlineStr">
+        <is>
+          <t>https://www.nictiz.nl/nieuws/</t>
+        </is>
+      </c>
+      <c r="S87" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — page lue le 24/09/2026 (pas de flux : /feed/ = 404) : dernier élément du 11/09/2026 ; articles datés 2026 sur l'EHDS (ex. https://www.nictiz.nl/nieuws/voorbereiden-op-de-ehds-regel-betrouwbare-toegang-met-eidas/, 15/07/2026). Article non ouvert individuellement (budget) : à confirmer au premier passage du script.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="152" t="inlineStr">
+        <is>
+          <t>Danemark</t>
+        </is>
+      </c>
+      <c r="B88" s="153" t="inlineStr">
+        <is>
+          <t>DKCERT (CERT danois de la recherche et de l'éducation) — actualités</t>
+        </is>
+      </c>
+      <c r="C88" s="154" t="n"/>
+      <c r="D88" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E88" s="155" t="inlineStr">
+        <is>
+          <t>https://www.cert.dk/</t>
+        </is>
+      </c>
+      <c r="F88" s="142" t="inlineStr">
+        <is>
+          <t>https://www.cert.dk/news/rss</t>
+        </is>
+      </c>
+      <c r="G88" s="128" t="n"/>
+      <c r="H88" s="153" t="n"/>
+      <c r="I88" s="153" t="n"/>
+      <c r="J88" s="156" t="n"/>
+      <c r="K88" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L88" s="157" t="n"/>
+      <c r="M88" s="157" t="n"/>
+      <c r="N88" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O88" s="159" t="n"/>
+      <c r="P88" s="153" t="n"/>
+      <c r="Q88" s="160" t="n"/>
+      <c r="R88" s="131" t="n"/>
+      <c r="S88" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe C — flux lu le 24/09/2026 : dernier élément du 24/09/2026 (RSS 2.0, actualités mêlées de quelques avis de vulnérabilité, dont des sujets réglementaires comme le CRA) ; article ouvert : https://www.cert.dk/news/2026-09-23/Automatiserede-angreb-rykker-hurtigere-end-det-automatiserede-forsvar</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="152" t="inlineStr">
+        <is>
+          <t>Finlande</t>
+        </is>
+      </c>
+      <c r="B89" s="153" t="inlineStr">
+        <is>
+          <t>Kanta-palvelut (services nationaux de données de santé, Kela) — actualités</t>
+        </is>
+      </c>
+      <c r="C89" s="154" t="n"/>
+      <c r="D89" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E89" s="155" t="inlineStr">
+        <is>
+          <t>https://www.kanta.fi/</t>
+        </is>
+      </c>
+      <c r="F89" s="142" t="n"/>
+      <c r="G89" s="128" t="n"/>
+      <c r="H89" s="153" t="n"/>
+      <c r="I89" s="153" t="n"/>
+      <c r="J89" s="156" t="n"/>
+      <c r="K89" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L89" s="157" t="n"/>
+      <c r="M89" s="157" t="n"/>
+      <c r="N89" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O89" s="159" t="n"/>
+      <c r="P89" s="153" t="n"/>
+      <c r="Q89" s="160" t="n"/>
+      <c r="R89" s="131" t="inlineStr">
+        <is>
+          <t>https://www.kanta.fi/ajankohtaista</t>
+        </is>
+      </c>
+      <c r="S89" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — page lue le 24/09/2026 : dernier élément du 22/09/2026 (liste datée, pas de flux RSS trouvé) ; article ouvert : https://www.kanta.fi/ajankohtaista/palvelinvarmenteisiin-muutoksia-1.10.2026-tarkista-kanta-liityntapisteesi-varmenteet (exigences de certificats serveur pour les points de connexion Kanta)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="152" t="inlineStr">
+        <is>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="B90" s="153" t="inlineStr">
+        <is>
+          <t>Norsk helsenett (NHN) — actualités</t>
+        </is>
+      </c>
+      <c r="C90" s="154" t="n"/>
+      <c r="D90" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E90" s="155" t="inlineStr">
+        <is>
+          <t>https://www.nhn.no/</t>
+        </is>
+      </c>
+      <c r="F90" s="142" t="n"/>
+      <c r="G90" s="128" t="n"/>
+      <c r="H90" s="153" t="n"/>
+      <c r="I90" s="153" t="n"/>
+      <c r="J90" s="156" t="n"/>
+      <c r="K90" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L90" s="157" t="n"/>
+      <c r="M90" s="157" t="n"/>
+      <c r="N90" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O90" s="159" t="n"/>
+      <c r="P90" s="153" t="n"/>
+      <c r="Q90" s="160" t="n"/>
+      <c r="R90" s="131" t="inlineStr">
+        <is>
+          <t>https://www.nhn.no/nyheter</t>
+        </is>
+      </c>
+      <c r="S90" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — page lue le 24/09/2026 : dernier élément du 17/09/2026 (pas de flux RSS) ; article ouvert : https://www.nhn.no/nyheter/endring-for-leverandorer-delegering-fra-helsevirksomheter-til-leverandorer-opprettes-pa-helsenettet.no (obligation de délégation aux fournisseurs via Helsenettet.no depuis le 25/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="152" t="inlineStr">
+        <is>
+          <t>Suède</t>
+        </is>
+      </c>
+      <c r="B91" s="153" t="inlineStr">
+        <is>
+          <t>eHälsomyndigheten (Agence suédoise de la santé numérique) — actualités</t>
+        </is>
+      </c>
+      <c r="C91" s="154" t="n"/>
+      <c r="D91" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E91" s="155" t="inlineStr">
+        <is>
+          <t>https://www.ehalsomyndigheten.se/</t>
+        </is>
+      </c>
+      <c r="F91" s="142" t="inlineStr">
+        <is>
+          <t>https://www.ehalsomyndigheten.se/om-ehalsomyndigheten/aktuellt/nyheter/rss</t>
+        </is>
+      </c>
+      <c r="G91" s="128" t="n"/>
+      <c r="H91" s="153" t="n"/>
+      <c r="I91" s="153" t="n"/>
+      <c r="J91" s="156" t="n"/>
+      <c r="K91" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L91" s="157" t="n"/>
+      <c r="M91" s="157" t="n"/>
+      <c r="N91" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O91" s="159" t="n"/>
+      <c r="P91" s="153" t="n"/>
+      <c r="Q91" s="160" t="n"/>
+      <c r="R91" s="131" t="inlineStr">
+        <is>
+          <t>https://www.ehalsomyndigheten.se/nyheter/</t>
+        </is>
+      </c>
+      <c r="S91" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux lu le 24/09/2026 : dernier élément du 23/09/2026 (Atom) ; article ouvert : https://www.ehalsomyndigheten.se/om-ehalsomyndigheten/aktuellt/nyheter/2026/webbinarier-stottar-sektorn-inforandet-av-ehds (EHDS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="152" t="inlineStr">
+        <is>
+          <t>Suède</t>
+        </is>
+      </c>
+      <c r="B92" s="153" t="inlineStr">
+        <is>
+          <t>Inera (services numériques communs des régions : 1177, NPÖ) — actualités</t>
+        </is>
+      </c>
+      <c r="C92" s="154" t="n"/>
+      <c r="D92" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E92" s="155" t="inlineStr">
+        <is>
+          <t>https://www.inera.se/</t>
+        </is>
+      </c>
+      <c r="F92" s="142" t="n"/>
+      <c r="G92" s="128" t="n"/>
+      <c r="H92" s="153" t="n"/>
+      <c r="I92" s="153" t="n"/>
+      <c r="J92" s="156" t="n"/>
+      <c r="K92" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L92" s="157" t="n"/>
+      <c r="M92" s="157" t="n"/>
+      <c r="N92" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O92" s="159" t="n"/>
+      <c r="P92" s="153" t="n"/>
+      <c r="Q92" s="160" t="n"/>
+      <c r="R92" s="131" t="inlineStr">
+        <is>
+          <t>https://www.inera.se/aktuellt/nyheter/</t>
+        </is>
+      </c>
+      <c r="S92" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — page lue le 24/09/2026 : dernier élément du 23/09/2026 (pas de flux RSS) ; article ouvert : https://www.inera.se/aktuellt/nyheter/kvantsakra-halsodata-kraver-forberedelser-redan-nu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="152" t="inlineStr">
+        <is>
+          <t>Rép. Tchèque</t>
+        </is>
+      </c>
+      <c r="B93" s="153" t="inlineStr">
+        <is>
+          <t>Ministerstvo zdravotnictví ČR (ministère de la santé)</t>
+        </is>
+      </c>
+      <c r="C93" s="154" t="n"/>
+      <c r="D93" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E93" s="155" t="inlineStr">
+        <is>
+          <t>https://mzd.gov.cz/</t>
+        </is>
+      </c>
+      <c r="F93" s="142" t="inlineStr">
+        <is>
+          <t>https://mzd.gov.cz/feed/</t>
+        </is>
+      </c>
+      <c r="G93" s="128" t="n"/>
+      <c r="H93" s="153" t="n"/>
+      <c r="I93" s="153" t="n"/>
+      <c r="J93" s="156" t="n"/>
+      <c r="K93" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L93" s="157" t="n"/>
+      <c r="M93" s="157" t="n"/>
+      <c r="N93" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O93" s="159" t="n"/>
+      <c r="P93" s="153" t="n"/>
+      <c r="Q93" s="160" t="n"/>
+      <c r="R93" s="131" t="n"/>
+      <c r="S93" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux lu le 24/09/2026 : dernier élément du 23/09/2026 (RSS 2.0 WordPress, tous les contenus du ministère, dont beaucoup d'appels d'offres de soins → bruit important, filtrage par mots-clés nécessaire) ; article ouvert : https://mzd.gov.cz/vyhlaseni-vyberoveho-rizeni-pred-uzavrenim-smlouvy-o-poskytovani-a-uhrade-hrazenych-sluzeb-jednodenni-pece-v-oboru-ortopedie-a-traumatologie-pohyboveho-ustroji-pro-uzemi-okresu-znojmo/</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="152" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="B94" s="153" t="inlineStr">
+        <is>
+          <t>Department of Health and Social Care (DHSC) – news &amp; communications</t>
+        </is>
+      </c>
+      <c r="C94" s="154" t="n"/>
+      <c r="D94" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E94" s="155" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/organisations/department-of-health-and-social-care</t>
+        </is>
+      </c>
+      <c r="F94" s="142" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/search/news-and-communications.atom?organisations[]=department-of-health-and-social-care</t>
+        </is>
+      </c>
+      <c r="G94" s="128" t="n"/>
+      <c r="H94" s="153" t="n"/>
+      <c r="I94" s="153" t="n"/>
+      <c r="J94" s="156" t="n"/>
+      <c r="K94" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L94" s="157" t="n"/>
+      <c r="M94" s="157" t="n"/>
+      <c r="N94" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O94" s="159" t="n"/>
+      <c r="P94" s="153" t="n"/>
+      <c r="Q94" s="160" t="n"/>
+      <c r="R94" s="131" t="n"/>
+      <c r="S94" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux Atom lu le 24/09/2026 : dernier élément du 17/09/2026 ; article ouvert : https://www.gov.uk/government/news/government-to-act-on-thirlwall-patient-safety-recommendations (gov.uk, même gabarit que l'article MHRA vérifié)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="152" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="B95" s="153" t="inlineStr">
+        <is>
+          <t>MHRA (Medicines and Healthcare products Regulatory Agency) – news &amp; communications</t>
+        </is>
+      </c>
+      <c r="C95" s="154" t="n"/>
+      <c r="D95" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E95" s="155" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/organisations/medicines-and-healthcare-products-regulatory-agency</t>
+        </is>
+      </c>
+      <c r="F95" s="142" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/search/news-and-communications.atom?organisations[]=medicines-and-healthcare-products-regulatory-agency</t>
+        </is>
+      </c>
+      <c r="G95" s="128" t="n"/>
+      <c r="H95" s="153" t="n"/>
+      <c r="I95" s="153" t="n"/>
+      <c r="J95" s="156" t="n"/>
+      <c r="K95" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L95" s="157" t="n"/>
+      <c r="M95" s="157" t="n"/>
+      <c r="N95" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O95" s="159" t="n"/>
+      <c r="P95" s="153" t="n"/>
+      <c r="Q95" s="160" t="n"/>
+      <c r="R95" s="131" t="n"/>
+      <c r="S95" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux Atom lu le 24/09/2026 : dernier élément du 16/09/2026 ; article ouvert : https://www.gov.uk/government/news/mhra-regulatory-reform-amendments-tabled-in-governments-health-bill (01/09/2026, amendements du Health Bill sur le futur régime de licence des dispositifs médicaux)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="152" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="B96" s="153" t="inlineStr">
+        <is>
+          <t>NHS England – news &amp; communications (via gov.uk)</t>
+        </is>
+      </c>
+      <c r="C96" s="154" t="n"/>
+      <c r="D96" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E96" s="155" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/organisations/nhs-england</t>
+        </is>
+      </c>
+      <c r="F96" s="142" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/search/news-and-communications.atom?organisations[]=nhs-england</t>
+        </is>
+      </c>
+      <c r="G96" s="128" t="n"/>
+      <c r="H96" s="153" t="n"/>
+      <c r="I96" s="153" t="n"/>
+      <c r="J96" s="156" t="n"/>
+      <c r="K96" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L96" s="157" t="n"/>
+      <c r="M96" s="157" t="n"/>
+      <c r="N96" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O96" s="159" t="n"/>
+      <c r="P96" s="153" t="n"/>
+      <c r="Q96" s="160" t="n"/>
+      <c r="R96" s="131" t="n"/>
+      <c r="S96" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux Atom lu le 24/09/2026 : dernier élément du 22/07/2026 (rythme faible : NHS England est en cours d'intégration au DHSC ; le site england.nhs.uk est inaccessible au robot) ; articles gov.uk lisibles (gabarit vérifié sur MHRA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="152" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="B97" s="153" t="inlineStr">
+        <is>
+          <t>NHS Innovation Service – News</t>
+        </is>
+      </c>
+      <c r="C97" s="154" t="n"/>
+      <c r="D97" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E97" s="155" t="inlineStr">
+        <is>
+          <t>https://innovation.nhs.uk/</t>
+        </is>
+      </c>
+      <c r="F97" s="142" t="n"/>
+      <c r="G97" s="128" t="n"/>
+      <c r="H97" s="153" t="n"/>
+      <c r="I97" s="153" t="n"/>
+      <c r="J97" s="156" t="n"/>
+      <c r="K97" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L97" s="157" t="n"/>
+      <c r="M97" s="157" t="n"/>
+      <c r="N97" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O97" s="159" t="n"/>
+      <c r="P97" s="153" t="n"/>
+      <c r="Q97" s="160" t="n"/>
+      <c r="R97" s="131" t="inlineStr">
+        <is>
+          <t>https://innovation.nhs.uk/news/</t>
+        </is>
+      </c>
+      <c r="S97" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — page lue le 24/09/2026 : liste datée, dernier élément du 14/09/2026, pas de flux RSS ; article ouvert : https://innovation.nhs.uk/news/2000-innovations-supported-through-the-nhs-innovation-service/ (10/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="152" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="B98" s="153" t="inlineStr">
+        <is>
+          <t>Cabinet Office – news &amp; communications (achats publics, sécurité gouvernementale)</t>
+        </is>
+      </c>
+      <c r="C98" s="154" t="n"/>
+      <c r="D98" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E98" s="155" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/government/organisations/cabinet-office</t>
+        </is>
+      </c>
+      <c r="F98" s="142" t="inlineStr">
+        <is>
+          <t>https://www.gov.uk/search/news-and-communications.atom?organisations[]=cabinet-office</t>
+        </is>
+      </c>
+      <c r="G98" s="128" t="n"/>
+      <c r="H98" s="153" t="n"/>
+      <c r="I98" s="153" t="n"/>
+      <c r="J98" s="156" t="n"/>
+      <c r="K98" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L98" s="157" t="n"/>
+      <c r="M98" s="157" t="n"/>
+      <c r="N98" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O98" s="159" t="n"/>
+      <c r="P98" s="153" t="n"/>
+      <c r="Q98" s="160" t="n"/>
+      <c r="R98" s="131" t="n"/>
+      <c r="S98" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe B — flux Atom lu le 24/09/2026 : dernier élément du 24/06/2026 (inclut 'Government procurement to prioritise national security', 19/06/2026) ; articles gov.uk lisibles (gabarit vérifié sur MHRA). Flux assez généraliste : prévoir un filtrage par mots-clés</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="152" t="inlineStr">
+        <is>
+          <t>Espagne</t>
+        </is>
+      </c>
+      <c r="B99" s="153" t="inlineStr">
+        <is>
+          <t>BOE – Boletín Oficial del Estado (Sección I, disposiciones generales)</t>
+        </is>
+      </c>
+      <c r="C99" s="154" t="n"/>
+      <c r="D99" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E99" s="155" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/</t>
+        </is>
+      </c>
+      <c r="F99" s="142" t="inlineStr">
+        <is>
+          <t>https://www.boe.es/rss/boe.php?s=1</t>
+        </is>
+      </c>
+      <c r="G99" s="128" t="n"/>
+      <c r="H99" s="153" t="n"/>
+      <c r="I99" s="153" t="n"/>
+      <c r="J99" s="156" t="n"/>
+      <c r="K99" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L99" s="157" t="n"/>
+      <c r="M99" s="157" t="n"/>
+      <c r="N99" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O99" s="159" t="n"/>
+      <c r="P99" s="153" t="n"/>
+      <c r="Q99" s="160" t="n"/>
+      <c r="R99" s="131" t="n"/>
+      <c r="S99" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe B — flux RSS lu le 24/09/2026 : dernier élément du 24/09/2026 ; article ouvert : https://www.boe.es/diario_boe/txt.php?id=BOE-A-2026-19762 (Orden HAC/988/2026). Filtrer sur 'Esquema Nacional de Seguridad', 'ciberseguridad', 'productos sanitarios', 'datos de salud'</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="152" t="inlineStr">
+        <is>
+          <t>Espagne</t>
+        </is>
+      </c>
+      <c r="B100" s="153" t="inlineStr">
+        <is>
+          <t>Ministerio de Sanidad – Notas de prensa</t>
+        </is>
+      </c>
+      <c r="C100" s="154" t="n"/>
+      <c r="D100" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E100" s="155" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/</t>
+        </is>
+      </c>
+      <c r="F100" s="142" t="n"/>
+      <c r="G100" s="128" t="n"/>
+      <c r="H100" s="153" t="n"/>
+      <c r="I100" s="153" t="n"/>
+      <c r="J100" s="156" t="n"/>
+      <c r="K100" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L100" s="157" t="n"/>
+      <c r="M100" s="157" t="n"/>
+      <c r="N100" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O100" s="159" t="n"/>
+      <c r="P100" s="153" t="n"/>
+      <c r="Q100" s="160" t="n"/>
+      <c r="R100" s="131" t="inlineStr">
+        <is>
+          <t>https://www.sanidad.gob.es/gabinete/notasPrensa.do</t>
+        </is>
+      </c>
+      <c r="S100" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — page lue le 24/09/2026 : liste datée, dernier élément du 22/09/2026 (un lien 'RSS' est affiché mais son URL n'a pas pu être extraite ; /rss/notasPrensa.xml = 404) ; article ouvert : https://www.sanidad.gob.es/gabinete/notasPrensa.do?id=6864 (05/03/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="152" t="inlineStr">
+        <is>
+          <t>Espagne</t>
+        </is>
+      </c>
+      <c r="B101" s="153" t="inlineStr">
+        <is>
+          <t>Red Seguridad (revue cyber espagnole)</t>
+        </is>
+      </c>
+      <c r="C101" s="154" t="n"/>
+      <c r="D101" s="153" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E101" s="155" t="inlineStr">
+        <is>
+          <t>https://www.redseguridad.com/</t>
+        </is>
+      </c>
+      <c r="F101" s="142" t="inlineStr">
+        <is>
+          <t>https://www.redseguridad.com/feed/</t>
+        </is>
+      </c>
+      <c r="G101" s="128" t="n"/>
+      <c r="H101" s="153" t="n"/>
+      <c r="I101" s="153" t="n"/>
+      <c r="J101" s="156" t="n"/>
+      <c r="K101" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L101" s="157" t="n"/>
+      <c r="M101" s="157" t="n"/>
+      <c r="N101" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O101" s="159" t="n"/>
+      <c r="P101" s="153" t="n"/>
+      <c r="Q101" s="160" t="n"/>
+      <c r="R101" s="131" t="n"/>
+      <c r="S101" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe D — flux RSS lu le 24/09/2026 : dernier élément du 22/09/2026 ; article ouvert : https://www.redseguridad.com/actualidad/ley-europea-eu-kids-limita-acceso-ninos-redes-sociales_20260921.html (21/09/2026). Couvre régulièrement ENS/NIS2 et réglementation UE</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="152" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B102" s="153" t="inlineStr">
+        <is>
+          <t>Agence du Numérique en Santé (ANS) — flux RSS</t>
+        </is>
+      </c>
+      <c r="C102" s="154" t="n"/>
+      <c r="D102" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E102" s="155" t="inlineStr">
+        <is>
+          <t>https://esante.gouv.fr/</t>
+        </is>
+      </c>
+      <c r="F102" s="142" t="inlineStr">
+        <is>
+          <t>https://esante.gouv.fr/rss.xml</t>
+        </is>
+      </c>
+      <c r="G102" s="128" t="n"/>
+      <c r="H102" s="153" t="n"/>
+      <c r="I102" s="153" t="n"/>
+      <c r="J102" s="156" t="n"/>
+      <c r="K102" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L102" s="157" t="n"/>
+      <c r="M102" s="157" t="n"/>
+      <c r="N102" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O102" s="159" t="n"/>
+      <c r="P102" s="153" t="n"/>
+      <c r="Q102" s="160" t="n"/>
+      <c r="R102" s="131" t="n"/>
+      <c r="S102" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux RSS lu (élément du 17/09/2026) ; articles protégés par un anti-robot mais lisibles dans un navigateur</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="152" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="B103" s="153" t="inlineStr">
+        <is>
+          <t>BfArM — communiqués (DiGA, dispositifs médicaux, logiciels)</t>
+        </is>
+      </c>
+      <c r="C103" s="154" t="n"/>
+      <c r="D103" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E103" s="155" t="inlineStr">
+        <is>
+          <t>https://www.bfarm.de/</t>
+        </is>
+      </c>
+      <c r="F103" s="142" t="inlineStr">
+        <is>
+          <t>https://www.bfarm.de/SiteGlobals/Functions/RSSFeed/DE/Pressemitteilungen/RSSNewsfeed.xml</t>
+        </is>
+      </c>
+      <c r="G103" s="128" t="n"/>
+      <c r="H103" s="153" t="n"/>
+      <c r="I103" s="153" t="n"/>
+      <c r="J103" s="156" t="n"/>
+      <c r="K103" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L103" s="157" t="n"/>
+      <c r="M103" s="157" t="n"/>
+      <c r="N103" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O103" s="159" t="n"/>
+      <c r="P103" s="153" t="n"/>
+      <c r="Q103" s="160" t="n"/>
+      <c r="R103" s="131" t="n"/>
+      <c r="S103" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 24/09/2026 : axe A — flux RSS lu (25/06/2026) ; texte de l'article non extrait par mon outil</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="152" t="inlineStr">
+        <is>
+          <t>Espagne</t>
+        </is>
+      </c>
+      <c r="B104" s="153" t="inlineStr">
+        <is>
+          <t>Computing España</t>
+        </is>
+      </c>
+      <c r="C104" s="154" t="n"/>
+      <c r="D104" s="153" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E104" s="155" t="inlineStr">
+        <is>
+          <t>https://www.computing.es/</t>
+        </is>
+      </c>
+      <c r="F104" s="142" t="inlineStr">
+        <is>
+          <t>https://www.computing.es/feed/</t>
+        </is>
+      </c>
+      <c r="G104" s="128" t="n"/>
+      <c r="H104" s="153" t="n"/>
+      <c r="I104" s="153" t="n"/>
+      <c r="J104" s="156" t="n"/>
+      <c r="K104" s="27" t="inlineStr">
+        <is>
+          <t>Actif - à confirmer</t>
+        </is>
+      </c>
+      <c r="L104" s="157" t="n"/>
+      <c r="M104" s="157" t="n"/>
+      <c r="N104" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O104" s="159" t="n"/>
+      <c r="P104" s="153" t="n"/>
+      <c r="Q104" s="160" t="n"/>
+      <c r="R104" s="131" t="n"/>
+      <c r="S104" s="131" t="inlineStr">
+        <is>
+          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="152" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="B105" s="153" t="inlineStr">
+        <is>
+          <t>ACN — Agenzia per la Cybersicurezza Nazionale (flux)</t>
+        </is>
+      </c>
+      <c r="C105" s="154" t="n"/>
+      <c r="D105" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E105" s="155" t="inlineStr">
+        <is>
+          <t>https://www.acn.gov.it/</t>
+        </is>
+      </c>
+      <c r="F105" s="142" t="inlineStr">
+        <is>
+          <t>https://www.acn.gov.it/portale/feedrss/-/journal/rss/20119/723192</t>
+        </is>
+      </c>
+      <c r="G105" s="128" t="n"/>
+      <c r="H105" s="153" t="n"/>
+      <c r="I105" s="153" t="n"/>
+      <c r="J105" s="156" t="n"/>
+      <c r="K105" s="27" t="inlineStr">
+        <is>
+          <t>Actif - à confirmer</t>
+        </is>
+      </c>
+      <c r="L105" s="157" t="n"/>
+      <c r="M105" s="157" t="n"/>
+      <c r="N105" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O105" s="159" t="n"/>
+      <c r="P105" s="153" t="n"/>
+      <c r="Q105" s="160" t="n"/>
+      <c r="R105" s="131" t="n"/>
+      <c r="S105" s="131" t="inlineStr">
+        <is>
+          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="152" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B106" s="153" t="inlineStr">
+        <is>
+          <t>CNCS — Centro Nacional de Cibersegurança (flux)</t>
+        </is>
+      </c>
+      <c r="C106" s="154" t="n"/>
+      <c r="D106" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E106" s="155" t="inlineStr">
+        <is>
+          <t>https://www.cncs.gov.pt/</t>
+        </is>
+      </c>
+      <c r="F106" s="142" t="inlineStr">
+        <is>
+          <t>https://www.cncs.gov.pt/docs/noticias/feed-rss/index.xml</t>
+        </is>
+      </c>
+      <c r="G106" s="128" t="n"/>
+      <c r="H106" s="153" t="n"/>
+      <c r="I106" s="153" t="n"/>
+      <c r="J106" s="156" t="n"/>
+      <c r="K106" s="27" t="inlineStr">
+        <is>
+          <t>Actif - à confirmer</t>
+        </is>
+      </c>
+      <c r="L106" s="157" t="n"/>
+      <c r="M106" s="157" t="n"/>
+      <c r="N106" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O106" s="159" t="n"/>
+      <c r="P106" s="153" t="n"/>
+      <c r="Q106" s="160" t="n"/>
+      <c r="R106" s="131" t="n"/>
+      <c r="S106" s="131" t="inlineStr">
+        <is>
+          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="152" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="B107" s="153" t="inlineStr">
+        <is>
+          <t>NHS England — site (flux WordPress)</t>
+        </is>
+      </c>
+      <c r="C107" s="154" t="n"/>
+      <c r="D107" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E107" s="155" t="inlineStr">
+        <is>
+          <t>https://www.england.nhs.uk/</t>
+        </is>
+      </c>
+      <c r="F107" s="142" t="inlineStr">
+        <is>
+          <t>https://www.england.nhs.uk/feed/</t>
+        </is>
+      </c>
+      <c r="G107" s="128" t="n"/>
+      <c r="H107" s="153" t="n"/>
+      <c r="I107" s="153" t="n"/>
+      <c r="J107" s="156" t="n"/>
+      <c r="K107" s="27" t="inlineStr">
+        <is>
+          <t>Actif - à confirmer</t>
+        </is>
+      </c>
+      <c r="L107" s="157" t="n"/>
+      <c r="M107" s="157" t="n"/>
+      <c r="N107" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O107" s="159" t="n"/>
+      <c r="P107" s="153" t="n"/>
+      <c r="Q107" s="160" t="n"/>
+      <c r="R107" s="131" t="n"/>
+      <c r="S107" s="131" t="inlineStr">
+        <is>
+          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="152" t="inlineStr">
+        <is>
+          <t>Royaume-Uni</t>
+        </is>
+      </c>
+      <c r="B108" s="153" t="inlineStr">
+        <is>
+          <t>Digital Health (presse santé numérique UK)</t>
+        </is>
+      </c>
+      <c r="C108" s="154" t="n"/>
+      <c r="D108" s="153" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E108" s="155" t="inlineStr">
+        <is>
+          <t>https://www.digitalhealth.net/</t>
+        </is>
+      </c>
+      <c r="F108" s="142" t="inlineStr">
+        <is>
+          <t>https://www.digitalhealth.net/feed/</t>
+        </is>
+      </c>
+      <c r="G108" s="128" t="n"/>
+      <c r="H108" s="153" t="n"/>
+      <c r="I108" s="153" t="n"/>
+      <c r="J108" s="156" t="n"/>
+      <c r="K108" s="27" t="inlineStr">
+        <is>
+          <t>Actif - à confirmer</t>
+        </is>
+      </c>
+      <c r="L108" s="157" t="n"/>
+      <c r="M108" s="157" t="n"/>
+      <c r="N108" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O108" s="159" t="n"/>
+      <c r="P108" s="153" t="n"/>
+      <c r="Q108" s="160" t="n"/>
+      <c r="R108" s="131" t="n"/>
+      <c r="S108" s="131" t="inlineStr">
+        <is>
+          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="152" t="inlineStr">
+        <is>
+          <t>Pologne</t>
+        </is>
+      </c>
+      <c r="B109" s="153" t="inlineStr">
+        <is>
+          <t>Centrum e-Zdrowia — aktualności</t>
+        </is>
+      </c>
+      <c r="C109" s="154" t="n"/>
+      <c r="D109" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E109" s="155" t="inlineStr">
+        <is>
+          <t>https://www.cez.gov.pl/</t>
+        </is>
+      </c>
+      <c r="F109" s="142" t="n"/>
+      <c r="G109" s="128" t="n"/>
+      <c r="H109" s="153" t="n"/>
+      <c r="I109" s="153" t="n"/>
+      <c r="J109" s="156" t="n"/>
+      <c r="K109" s="27" t="inlineStr">
+        <is>
+          <t>Actif - à confirmer</t>
+        </is>
+      </c>
+      <c r="L109" s="157" t="n"/>
+      <c r="M109" s="157" t="n"/>
+      <c r="N109" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O109" s="159" t="n"/>
+      <c r="P109" s="153" t="n"/>
+      <c r="Q109" s="160" t="n"/>
+      <c r="R109" s="131" t="inlineStr">
+        <is>
+          <t>https://www.cez.gov.pl/pl/page/o-nas/aktualnosci</t>
+        </is>
+      </c>
+      <c r="S109" s="131" t="inlineStr">
+        <is>
+          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="152" t="inlineStr">
+        <is>
+          <t>Espagne</t>
+        </is>
+      </c>
+      <c r="B110" s="153" t="inlineStr">
+        <is>
+          <t>CCN — Actualidad (portail ccn.cni.es : ENS, catalogue CPSTIC, qualifications)</t>
+        </is>
+      </c>
+      <c r="C110" s="154" t="n"/>
+      <c r="D110" s="153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E110" s="155" t="inlineStr">
+        <is>
+          <t>https://www.ccn.cni.es/</t>
+        </is>
+      </c>
+      <c r="F110" s="142" t="n"/>
+      <c r="G110" s="128" t="n"/>
+      <c r="H110" s="153" t="n"/>
+      <c r="I110" s="153" t="n"/>
+      <c r="J110" s="156" t="n"/>
+      <c r="K110" s="27" t="inlineStr">
+        <is>
+          <t>Actif - à confirmer</t>
+        </is>
+      </c>
+      <c r="L110" s="157" t="n"/>
+      <c r="M110" s="157" t="n"/>
+      <c r="N110" s="158" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+      <c r="O110" s="159" t="n"/>
+      <c r="P110" s="153" t="n"/>
+      <c r="Q110" s="160" t="n"/>
+      <c r="R110" s="131" t="inlineStr">
+        <is>
+          <t>https://www.ccn.cni.es/es/actualidad-ccn</t>
+        </is>
+      </c>
+      <c r="S110" s="131" t="inlineStr">
+        <is>
+          <t>À tester en conditions réelles : page trouvée par la recherche du 24/09/2026 (mise à jour CPSTIC du 27/07/2026), non relue par mon outil.</t>
         </is>
       </c>
     </row>

--- a/config/sources.xlsx
+++ b/config/sources.xlsx
@@ -2030,7 +2030,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourcesCyberwatch12" displayName="SourcesCyberwatch12" ref="A1:T110" headerRowCount="1" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SourcesCyberwatch12" displayName="SourcesCyberwatch12" ref="A1:T125" headerRowCount="1" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
   <autoFilter ref="A1:S79"/>
   <sortState ref="A2:Q41">
     <sortCondition ref="A1:A41"/>
@@ -4656,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T110"/>
+  <dimension ref="A1:T125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.1796875" customWidth="1" min="1" max="1"/>
@@ -11605,6 +11605,904 @@
       <c r="S110" s="131" t="inlineStr">
         <is>
           <t>À tester en conditions réelles : page trouvée par la recherche du 24/09/2026 (mise à jour CPSTIC du 27/07/2026), non relue par mon outil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B111" s="153" t="inlineStr">
+        <is>
+          <t>EDRi (European Digital Rights)</t>
+        </is>
+      </c>
+      <c r="C111" s="154" t="n"/>
+      <c r="D111" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E111" s="155" t="inlineStr">
+        <is>
+          <t>https://edri.org/</t>
+        </is>
+      </c>
+      <c r="F111" s="142" t="inlineStr">
+        <is>
+          <t>https://edri.org/feed/</t>
+        </is>
+      </c>
+      <c r="G111" s="128" t="n"/>
+      <c r="H111" s="153" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="I111" s="153" t="n"/>
+      <c r="J111" s="156" t="n"/>
+      <c r="K111" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L111" s="157" t="n"/>
+      <c r="M111" s="157" t="n"/>
+      <c r="N111" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O111" s="159" t="n"/>
+      <c r="P111" s="153" t="n"/>
+      <c r="Q111" s="160" t="n"/>
+      <c r="R111" s="131" t="n"/>
+      <c r="S111" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : flux lu le 25/09/2026 : dernier élément du 24/09/2026 ; exemple : Simplification for whom? Open letter to EU Member States to uphold GDPR protections in Digital Omnibus on Data</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B112" s="153" t="inlineStr">
+        <is>
+          <t>CERRE (Centre on Regulation in Europe)</t>
+        </is>
+      </c>
+      <c r="C112" s="154" t="n"/>
+      <c r="D112" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E112" s="155" t="inlineStr">
+        <is>
+          <t>https://cerre.eu/</t>
+        </is>
+      </c>
+      <c r="F112" s="142" t="n"/>
+      <c r="G112" s="128" t="n"/>
+      <c r="H112" s="153" t="inlineStr">
+        <is>
+          <t>think tank</t>
+        </is>
+      </c>
+      <c r="I112" s="153" t="n"/>
+      <c r="J112" s="156" t="n"/>
+      <c r="K112" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L112" s="157" t="n"/>
+      <c r="M112" s="157" t="n"/>
+      <c r="N112" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O112" s="159" t="n"/>
+      <c r="P112" s="153" t="n"/>
+      <c r="Q112" s="160" t="n"/>
+      <c r="R112" s="131" t="inlineStr">
+        <is>
+          <t>https://cerre.eu/publications/</t>
+        </is>
+      </c>
+      <c r="S112" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (flux https://cerre.eu/feed/ vide, ne pas l'utiliser) : dernier élément du 08/09/2026 ; exemples : Rules for High-Risk AI Systems under the AI Act (22/06/2026), Making Data Protection Fit for the Age of AI (18/06/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B113" s="153" t="inlineStr">
+        <is>
+          <t>DIGITALEUROPE - positions</t>
+        </is>
+      </c>
+      <c r="C113" s="154" t="n"/>
+      <c r="D113" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E113" s="155" t="inlineStr">
+        <is>
+          <t>https://www.digitaleurope.org/</t>
+        </is>
+      </c>
+      <c r="F113" s="142" t="n"/>
+      <c r="G113" s="128" t="n"/>
+      <c r="H113" s="153" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="I113" s="153" t="n"/>
+      <c r="J113" s="156" t="n"/>
+      <c r="K113" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L113" s="157" t="n"/>
+      <c r="M113" s="157" t="n"/>
+      <c r="N113" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O113" s="159" t="n"/>
+      <c r="P113" s="153" t="n"/>
+      <c r="Q113" s="160" t="n"/>
+      <c r="R113" s="131" t="inlineStr">
+        <is>
+          <t>https://www.digitaleurope.org/resources/</t>
+        </is>
+      </c>
+      <c r="S113" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (flux /feed/ vide) : dernier élément du 23/06/2026 ; exemples : A practical path to EU-US cybersecurity mutual recognition ; AI in healthcare policy paper (08/06/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B114" s="153" t="inlineStr">
+        <is>
+          <t>ECIPE (European Centre for International Political Economy)</t>
+        </is>
+      </c>
+      <c r="C114" s="154" t="n"/>
+      <c r="D114" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E114" s="155" t="inlineStr">
+        <is>
+          <t>https://ecipe.org/</t>
+        </is>
+      </c>
+      <c r="F114" s="142" t="inlineStr">
+        <is>
+          <t>https://ecipe.org/feed/</t>
+        </is>
+      </c>
+      <c r="G114" s="128" t="n"/>
+      <c r="H114" s="153" t="inlineStr">
+        <is>
+          <t>think tank</t>
+        </is>
+      </c>
+      <c r="I114" s="153" t="n"/>
+      <c r="J114" s="156" t="n"/>
+      <c r="K114" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L114" s="157" t="n"/>
+      <c r="M114" s="157" t="n"/>
+      <c r="N114" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O114" s="159" t="n"/>
+      <c r="P114" s="153" t="n"/>
+      <c r="Q114" s="160" t="n"/>
+      <c r="R114" s="131" t="n"/>
+      <c r="S114" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : flux lu le 25/09/2026 : dernier élément du 31/08/2026 ; exemple : Steering into Price Control: Why the CMA's App-Store Proposals Go beyond What is Necessary (28/07/2026). Pertinence : régulation numérique/commerce, filtrer par mots-clés</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B115" s="153" t="inlineStr">
+        <is>
+          <t>European Policy Centre (EPC)</t>
+        </is>
+      </c>
+      <c r="C115" s="154" t="n"/>
+      <c r="D115" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E115" s="155" t="inlineStr">
+        <is>
+          <t>https://www.epc.eu/</t>
+        </is>
+      </c>
+      <c r="F115" s="142" t="n"/>
+      <c r="G115" s="128" t="n"/>
+      <c r="H115" s="153" t="inlineStr">
+        <is>
+          <t>think tank</t>
+        </is>
+      </c>
+      <c r="I115" s="153" t="n"/>
+      <c r="J115" s="156" t="n"/>
+      <c r="K115" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L115" s="157" t="n"/>
+      <c r="M115" s="157" t="n"/>
+      <c r="N115" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O115" s="159" t="n"/>
+      <c r="P115" s="153" t="n"/>
+      <c r="Q115" s="160" t="n"/>
+      <c r="R115" s="131" t="inlineStr">
+        <is>
+          <t>https://www.epc.eu/en/Publications/</t>
+        </is>
+      </c>
+      <c r="S115" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux RSS) : dernier élément du 24/09/2026 ; exemple : Europe's security moment: Time to widen the options. Généraliste, filtrer par mots-clés numérique/cyber</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B116" s="153" t="inlineStr">
+        <is>
+          <t>Bruegel - Analysis</t>
+        </is>
+      </c>
+      <c r="C116" s="154" t="n"/>
+      <c r="D116" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E116" s="155" t="inlineStr">
+        <is>
+          <t>https://www.bruegel.org/</t>
+        </is>
+      </c>
+      <c r="F116" s="142" t="n"/>
+      <c r="G116" s="128" t="n"/>
+      <c r="H116" s="153" t="inlineStr">
+        <is>
+          <t>think tank</t>
+        </is>
+      </c>
+      <c r="I116" s="153" t="n"/>
+      <c r="J116" s="156" t="n"/>
+      <c r="K116" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L116" s="157" t="n"/>
+      <c r="M116" s="157" t="n"/>
+      <c r="N116" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O116" s="159" t="n"/>
+      <c r="P116" s="153" t="n"/>
+      <c r="Q116" s="160" t="n"/>
+      <c r="R116" s="131" t="inlineStr">
+        <is>
+          <t>https://www.bruegel.org/analysis</t>
+        </is>
+      </c>
+      <c r="S116" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 17/09/2026 ; exemple : China's artificial intelligence goals and strategic choices for Europe (10/09/2026). Ne pas utiliser rss.xml (sessions d'événements). Pertinence cyber faible, filtrer</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="152" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B117" s="153" t="inlineStr">
+        <is>
+          <t>CESIN (Club des experts de la sécurité de l'information et du numérique)</t>
+        </is>
+      </c>
+      <c r="C117" s="154" t="n"/>
+      <c r="D117" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E117" s="155" t="inlineStr">
+        <is>
+          <t>https://www.cesin.fr/</t>
+        </is>
+      </c>
+      <c r="F117" s="142" t="n"/>
+      <c r="G117" s="128" t="n"/>
+      <c r="H117" s="153" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="I117" s="153" t="n"/>
+      <c r="J117" s="156" t="n"/>
+      <c r="K117" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L117" s="157" t="n"/>
+      <c r="M117" s="157" t="n"/>
+      <c r="N117" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O117" s="159" t="n"/>
+      <c r="P117" s="153" t="n"/>
+      <c r="Q117" s="160" t="n"/>
+      <c r="R117" s="131" t="inlineStr">
+        <is>
+          <t>https://cesin.fr/articles/?idTheme=3</t>
+        </is>
+      </c>
+      <c r="S117" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 22/09/2026 ; exemples : IA, réglementation, dépendances, les RSSI doivent arbitrer sur tous les fronts (18/09/2026) ; Lettre ouverte Présidentielle 2027 souveraineté numérique et cybersécurité (09/07/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="152" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="B118" s="153" t="inlineStr">
+        <is>
+          <t>Future of Privacy Forum (FPF)</t>
+        </is>
+      </c>
+      <c r="C118" s="154" t="n"/>
+      <c r="D118" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E118" s="155" t="inlineStr">
+        <is>
+          <t>https://fpf.org/</t>
+        </is>
+      </c>
+      <c r="F118" s="142" t="inlineStr">
+        <is>
+          <t>https://fpf.org/feed/</t>
+        </is>
+      </c>
+      <c r="G118" s="128" t="n"/>
+      <c r="H118" s="153" t="inlineStr">
+        <is>
+          <t>think tank</t>
+        </is>
+      </c>
+      <c r="I118" s="153" t="n"/>
+      <c r="J118" s="156" t="n"/>
+      <c r="K118" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L118" s="157" t="n"/>
+      <c r="M118" s="157" t="n"/>
+      <c r="N118" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O118" s="159" t="n"/>
+      <c r="P118" s="153" t="n"/>
+      <c r="Q118" s="160" t="n"/>
+      <c r="R118" s="131" t="n"/>
+      <c r="S118" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : flux lu le 25/09/2026 : dernier élément du 24/09/2026 ; exemple : New FPF Report Analyzes the Rise in Chatbot Legislation &amp; What's Ahead (23/09/2026). Contenu majoritairement US, garder les éléments EU/UK</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B119" s="153" t="inlineStr">
+        <is>
+          <t>Taylor Wessing - Insights</t>
+        </is>
+      </c>
+      <c r="C119" s="154" t="n"/>
+      <c r="D119" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E119" s="155" t="inlineStr">
+        <is>
+          <t>https://www.taylorwessing.com/</t>
+        </is>
+      </c>
+      <c r="F119" s="142" t="n"/>
+      <c r="G119" s="128" t="n"/>
+      <c r="H119" s="153" t="inlineStr">
+        <is>
+          <t>cabinet</t>
+        </is>
+      </c>
+      <c r="I119" s="153" t="n"/>
+      <c r="J119" s="156" t="n"/>
+      <c r="K119" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L119" s="157" t="n"/>
+      <c r="M119" s="157" t="n"/>
+      <c r="N119" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O119" s="159" t="n"/>
+      <c r="P119" s="153" t="n"/>
+      <c r="Q119" s="160" t="n"/>
+      <c r="R119" s="131" t="inlineStr">
+        <is>
+          <t>https://www.taylorwessing.com/en/insights-and-events/insights</t>
+        </is>
+      </c>
+      <c r="S119" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux) : dernier élément affiché du 29/05/2026 ; exemples : Cyber Resilience Act and Franchise Networks ; Physical AI in the Digital Omnibus – Update (27/05/2026). Liste peut-être incomplète, à surveiller</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="152" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="B120" s="153" t="inlineStr">
+        <is>
+          <t>Hogan Lovells (HLC) - Our thinking</t>
+        </is>
+      </c>
+      <c r="C120" s="154" t="n"/>
+      <c r="D120" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E120" s="155" t="inlineStr">
+        <is>
+          <t>https://www.hlc.com/en/our-thinking</t>
+        </is>
+      </c>
+      <c r="F120" s="142" t="inlineStr">
+        <is>
+          <t>https://www.hlc.com/rss/rss?id={85A6BA7F-0842-47CB-BF5E-8AEF326CC650}</t>
+        </is>
+      </c>
+      <c r="G120" s="128" t="inlineStr">
+        <is>
+          <t>https://www.hlc.com/rss/rss?id={23D3816F-56DB-4796-A0D3-1D0CF5C914BF}</t>
+        </is>
+      </c>
+      <c r="H120" s="153" t="inlineStr">
+        <is>
+          <t>cabinet</t>
+        </is>
+      </c>
+      <c r="I120" s="153" t="n"/>
+      <c r="J120" s="156" t="n"/>
+      <c r="K120" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L120" s="157" t="n"/>
+      <c r="M120" s="157" t="n"/>
+      <c r="N120" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O120" s="159" t="n"/>
+      <c r="P120" s="153" t="n"/>
+      <c r="Q120" s="160" t="n"/>
+      <c r="R120" s="131" t="inlineStr">
+        <is>
+          <t>https://www.hlc.com/en/our-thinking</t>
+        </is>
+      </c>
+      <c r="S120" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 04/09/2026 ; exemple : Same passport, different rules? The UK's digital product record call for evidence and the future of UK-EU product regulation (01/09/2026). Flux Privacy/Cyber et Life Sciences listés sur https://www.hlc.com/en/rss mais non lus (budget) : à tester avant activation ; hoganlovells.com redirige vers hlc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B121" s="153" t="inlineStr">
+        <is>
+          <t>MedTech Europe (association européenne des technologies médicales et du DIV)</t>
+        </is>
+      </c>
+      <c r="C121" s="154" t="n"/>
+      <c r="D121" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E121" s="155" t="inlineStr">
+        <is>
+          <t>https://www.medtecheurope.org/news-and-events/news/</t>
+        </is>
+      </c>
+      <c r="F121" s="142" t="inlineStr">
+        <is>
+          <t>https://www.medtecheurope.org/feed/</t>
+        </is>
+      </c>
+      <c r="G121" s="128" t="n"/>
+      <c r="H121" s="153" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="I121" s="153" t="n"/>
+      <c r="J121" s="156" t="n"/>
+      <c r="K121" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L121" s="157" t="n"/>
+      <c r="M121" s="157" t="n"/>
+      <c r="N121" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O121" s="159" t="n"/>
+      <c r="P121" s="153" t="n"/>
+      <c r="Q121" s="160" t="n"/>
+      <c r="R121" s="131" t="inlineStr">
+        <is>
+          <t>https://www.medtecheurope.org/news-and-events/news/</t>
+        </is>
+      </c>
+      <c r="S121" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : flux lu le 25/09/2026 : dernier élément du 11/09/2026 ; exemple : MedTech Europe responds to stakeholder consultation on the classification of high-risk AI systems (aussi : EU Joint Clinical Assessment for medical technologies – Ready to launch?, 02/07/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B122" s="153" t="inlineStr">
+        <is>
+          <t>COCIR (industrie européenne de l'imagerie médicale, de la radiothérapie et de la santé numérique) – Position papers</t>
+        </is>
+      </c>
+      <c r="C122" s="154" t="n"/>
+      <c r="D122" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E122" s="155" t="inlineStr">
+        <is>
+          <t>https://www.cocir.org/position/</t>
+        </is>
+      </c>
+      <c r="F122" s="142" t="n"/>
+      <c r="G122" s="128" t="n"/>
+      <c r="H122" s="153" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="I122" s="153" t="n"/>
+      <c r="J122" s="156" t="n"/>
+      <c r="K122" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L122" s="157" t="n"/>
+      <c r="M122" s="157" t="n"/>
+      <c r="N122" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O122" s="159" t="n"/>
+      <c r="P122" s="153" t="n"/>
+      <c r="Q122" s="160" t="n"/>
+      <c r="R122" s="131" t="inlineStr">
+        <is>
+          <t>https://www.cocir.org/position/</t>
+        </is>
+      </c>
+      <c r="S122" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux RSS exploitable : /feed renvoie du HTML, /news/ est un gabarit vide) : dernier élément du 10/08/2026 ; exemples : Joint position: Smarter MDR and IVDR oversight (23/06/2026), Targeted revision of EU MDR Rule 11 for medical device software (30/04/2026), Joint industry statement on the AI omnibus (12/03/2026), Safeguarding IP and trade secrets in the EHDS (15/01/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="152" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="B123" s="153" t="inlineStr">
+        <is>
+          <t>BVMed (Bundesverband Medizintechnologie) – Regulatorik / MDR</t>
+        </is>
+      </c>
+      <c r="C123" s="154" t="n"/>
+      <c r="D123" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E123" s="155" t="inlineStr">
+        <is>
+          <t>https://www.bvmed.de/themen/regulatorik-mdr</t>
+        </is>
+      </c>
+      <c r="F123" s="142" t="n"/>
+      <c r="G123" s="128" t="n"/>
+      <c r="H123" s="153" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="I123" s="153" t="n"/>
+      <c r="J123" s="156" t="n"/>
+      <c r="K123" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L123" s="157" t="n"/>
+      <c r="M123" s="157" t="n"/>
+      <c r="N123" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O123" s="159" t="n"/>
+      <c r="P123" s="153" t="n"/>
+      <c r="Q123" s="160" t="n"/>
+      <c r="R123" s="131" t="inlineStr">
+        <is>
+          <t>https://www.bvmed.de/themen/regulatorik-mdr
+https://www.bvmed.de/de/bvmed/presse/pressemeldungen</t>
+        </is>
+      </c>
+      <c r="S123" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 16/09/2026 ; exemples : Rede zur Lage der EU: KI und Gesundheit im Fokus, aber mit effizienter Regulierung (16/09/2026), KI-Verordnung: Was jetzt gilt und was der KI-Omnibus verschoben hat (30/07/2026), Stellungnahme: Medizinprodukte und In-vitro-Diagnostika – gezielte Überarbeitung der EU-Vorschriften (16/07/2026). Flux RSS existant mais URL générée par formulaire (https://www.bvmed.de/rss) : non récupérée, à générer à la main</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="152" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B124" s="153" t="inlineStr">
+        <is>
+          <t>Inside EU Life Sciences (blog Covington &amp; Burling)</t>
+        </is>
+      </c>
+      <c r="C124" s="154" t="n"/>
+      <c r="D124" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E124" s="155" t="inlineStr">
+        <is>
+          <t>https://www.insideeulifesciences.com/</t>
+        </is>
+      </c>
+      <c r="F124" s="142" t="inlineStr">
+        <is>
+          <t>https://www.insideeulifesciences.com/feed</t>
+        </is>
+      </c>
+      <c r="G124" s="128" t="n"/>
+      <c r="H124" s="153" t="inlineStr">
+        <is>
+          <t>cabinet</t>
+        </is>
+      </c>
+      <c r="I124" s="153" t="n"/>
+      <c r="J124" s="156" t="n"/>
+      <c r="K124" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L124" s="157" t="n"/>
+      <c r="M124" s="157" t="n"/>
+      <c r="N124" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O124" s="159" t="n"/>
+      <c r="P124" s="153" t="n"/>
+      <c r="Q124" s="160" t="n"/>
+      <c r="R124" s="131" t="inlineStr">
+        <is>
+          <t>https://www.insideeulifesciences.com/</t>
+        </is>
+      </c>
+      <c r="S124" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page d'accueil lue le 25/09/2026 (flux annoncé, non ouvert directement : autorisation de fetch non accordée) : dernier élément du 02/09/2026 ; exemples : The Proposed EU Biotech Act: New Biosecurity Rules for AI and Biotechnology Companies (02/09/2026), New UK Guidance Clarifies Medical Device Status of AI Scribes (06/08/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="152" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="B125" s="153" t="inlineStr">
+        <is>
+          <t>Johner Institut – blog regulatory affairs (MDR/IVDR, AI Act, cybersécurité DM)</t>
+        </is>
+      </c>
+      <c r="C125" s="154" t="n"/>
+      <c r="D125" s="153" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E125" s="155" t="inlineStr">
+        <is>
+          <t>https://blog.johner-institute.com/tag/mdr/</t>
+        </is>
+      </c>
+      <c r="F125" s="142" t="n"/>
+      <c r="G125" s="128" t="n"/>
+      <c r="H125" s="153" t="inlineStr">
+        <is>
+          <t>cabinet</t>
+        </is>
+      </c>
+      <c r="I125" s="153" t="n"/>
+      <c r="J125" s="156" t="n"/>
+      <c r="K125" s="27" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L125" s="157" t="n"/>
+      <c r="M125" s="157" t="n"/>
+      <c r="N125" s="158" t="inlineStr">
+        <is>
+          <t>25/09/2026</t>
+        </is>
+      </c>
+      <c r="O125" s="159" t="n"/>
+      <c r="P125" s="153" t="n"/>
+      <c r="Q125" s="160" t="n"/>
+      <c r="R125" s="131" t="inlineStr">
+        <is>
+          <t>https://blog.johner-institute.com/tag/mdr/
+https://www.johner-institut.de/blog/</t>
+        </is>
+      </c>
+      <c r="S125" s="131" t="inlineStr">
+        <is>
+          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 14/04/2026 ; exemple : MDR 2.0, IVDR 2.0: What the Commission is planning (15/01/2026), MDR Classification Rule 11: The classification nightmare? (21/01/2026). Cabinet de conseil (pas d'avocats). Flux RSS non confirmé ; rythme de publication lent</t>
         </is>
       </c>
     </row>

--- a/config/sources.xlsx
+++ b/config/sources.xlsx
@@ -4656,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T125"/>
+  <dimension ref="A1:T131"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.1796875" customWidth="1" min="1" max="1"/>
@@ -4805,11 +4805,7 @@
           <t>https://www.bsi.bund.de/EN/Home/home_node.html</t>
         </is>
       </c>
-      <c r="F2" s="129" t="inlineStr">
-        <is>
-          <t>https://wid.cert-bund.de/content/public/securityAdvisory/rss</t>
-        </is>
-      </c>
+      <c r="F2" s="129" t="n"/>
       <c r="G2" s="130" t="n"/>
       <c r="H2" s="7" t="inlineStr">
         <is>
@@ -4852,7 +4848,7 @@
       </c>
       <c r="S2" s="131" t="inlineStr">
         <is>
-          <t>Flux Presse + pages presse, NIS2, CRA, Technische Richtlinien. Flux CERT-Bund (alertes) gardé en 2e. (recherche du 23/09/2026)
+          <t>v4 (28/09/2026) : flux WID (alertes de vulnérabilités, ~450/mois) retiré ; seules les pages presse sont surveillées. | Flux Presse + pages presse, NIS2, CRA, Technische Richtlinien. Flux CERT-Bund (alertes) gardé en 2e. (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.bsi.bund.de/DE/Service-Navi/Presse/presse_node.html (page d'accueil presse sans dates)
 - https://www.bsi.bund.de/DE/Themen/Regulierte-Wirtschaft/NIS-2-regulierte-Unternehmen/nis-2-regulierte-unternehmen_node.html (page thématique sans dates)
@@ -5237,7 +5233,7 @@
       </c>
       <c r="K8" s="115" t="inlineStr">
         <is>
-          <t>Actif - à confirmer</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L8" s="116" t="inlineStr">
@@ -5265,7 +5261,7 @@
       </c>
       <c r="S8" s="131" t="inlineStr">
         <is>
-          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+          <t>v4 (28/09/2026) : retirée : bloque les robots (aucun article lu lors de la collecte GitHub du 25/09/2026). | À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5488,12 @@
           <t>https://eur-lex.europa.eu/homepage.html?locale=fr</t>
         </is>
       </c>
-      <c r="F12" s="136" t="n"/>
+      <c r="F12" s="136" t="inlineStr">
+        <is>
+          <t>https://eur-lex.europa.eu/EN/display-feed.rss?rssId=222
+https://eur-lex.europa.eu/EN/display-feed.rss?rssId=166</t>
+        </is>
+      </c>
       <c r="G12" s="137" t="n"/>
       <c r="H12" s="9" t="inlineStr">
         <is>
@@ -5507,7 +5508,7 @@
       </c>
       <c r="K12" s="29" t="inlineStr">
         <is>
-          <t>Actif (pas de flux actus dédié)</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="L12" s="17" t="inlineStr">
@@ -5531,7 +5532,12 @@
       <c r="R12" s="131" t="n"/>
       <c r="S12" s="131" t="inlineStr">
         <is>
-          <t>Base juridique, pas de page actualités : conservée en l'état.</t>
+          <t>v4 (28/09/2026) : flux RSS du Journal officiel de l'UE, série L (actes) et série C (communications) ; filtrage « pertinence ». | Base juridique, pas de page actualités : conservée en l'état.</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5998,7 @@
       <c r="C20" s="76" t="n"/>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>Experts officiels de la Commission Européenne</t>
+          <t>Site institutionnel officiel (groupe d'experts de la Commission)</t>
         </is>
       </c>
       <c r="E20" s="83" t="inlineStr">
@@ -6000,11 +6006,7 @@
           <t>https://health.ec.europa.eu/medical-devices-sector/new-regulations/guidance-mdcg-endorsed-documents-and-other-guidance_en</t>
         </is>
       </c>
-      <c r="F20" s="136" t="inlineStr">
-        <is>
-          <t>https://health.ec.europa.eu/node/2/rss_en</t>
-        </is>
-      </c>
+      <c r="F20" s="136" t="n"/>
       <c r="G20" s="137" t="n"/>
       <c r="H20" s="7" t="inlineStr">
         <is>
@@ -6042,13 +6044,12 @@
       </c>
       <c r="R20" s="141" t="inlineStr">
         <is>
-          <t>https://health.ec.europa.eu/medical-devices-sector/new-regulations/guidance-mdcg-endorsed-documents-and-other-guidance_en
-https://health.ec.europa.eu/latest-updates_en</t>
+          <t>https://health.ec.europa.eu/medical-devices-sector/new-regulations/guidance-mdcg-endorsed-documents-and-other-guidance_en</t>
         </is>
       </c>
       <c r="S20" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 02/07/2026 (le flux semble en retard sur la page, dont le dernier élément est du 18/09/2026 : garder la page en secours) ; article ouvert : https://health.ec.europa.eu/latest-updates/three-new-templates-support-written-input-patients-carers-and-clinicians-joint-clinical-assessments-2026-09-14_en. Couvre EHDS, HTA, organismes notifiés DM/DIV ; volume modéré, beaucoup d'éléments hors cyber.</t>
+          <t>v4 (28/09/2026) : flux DG SANTE retiré (collé par erreur sur cette ligne) ; seule la page des guidances MDCG est surveillée ; type corrigé (n'est pas un « avis d'expert »). | Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 02/07/2026 (le flux semble en retard sur la page, dont le dernier élément est du 18/09/2026 : garder la page en secours) ; article ouvert : https://health.ec.europa.eu/latest-updates/three-new-templates-support-written-input-patients-carers-and-clinicians-joint-clinical-assessments-2026-09-14_en. Couvre EHDS, HTA, organismes notifiés DM/DIV ; volume modéré, beaucoup d'éléments hors cyber.</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6163,7 @@
       </c>
       <c r="K22" s="29" t="inlineStr">
         <is>
-          <t>Actif (base juridique, pas un flux d'actus)</t>
+          <t>Actif</t>
         </is>
       </c>
       <c r="L22" s="17" t="inlineStr">
@@ -6186,7 +6187,12 @@
       <c r="R22" s="131" t="n"/>
       <c r="S22" s="131" t="inlineStr">
         <is>
-          <t>Collecte via l'API officielle Légifrance (PISTE) dès que les identifiants sont ajoutés aux secrets GitHub (voir README). Sans identifiants : « non configurée » dans l'État des sources.</t>
+          <t>v4 (28/09/2026) : collecte via les données ouvertes de la DILA (archives quotidiennes du JO, sans compte ni clé) ; mesures individuelles écartées ; filtrage « pertinence ». | Collecte via l'API officielle Légifrance (PISTE) dès que les identifiants sont ajoutés aux secrets GitHub (voir README). Sans identifiants : « non configurée » dans l'État des sources.</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7192,12 @@
       </c>
       <c r="S36" s="131" t="inlineStr">
         <is>
-          <t>Liste des actualités vérifiée (dernière le 22/09/2026). Filtres par thème non exploitables en URL fixe. (recherche du 23/09/2026)</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (presse vie privée internationale, volume élevé). | Liste des actualités vérifiée (dernière le 22/09/2026). Filtres par thème non exploitables en URL fixe. (recherche du 23/09/2026)</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -7313,9 +7324,14 @@
       </c>
       <c r="S38" s="131" t="inlineStr">
         <is>
-          <t>Communiqués (vérifiés) + page DORA + publications ; flux RSS repéré. (recherche du 23/09/2026)
+          <t>v4 (28/09/2026) : filtrage « pertinence » (finance/banque, volume élevé). | Communiqués (vérifiés) + page DORA + publications ; flux RSS repéré. (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.eba.europa.eu/activities/direct-supervision-and-oversight/digital-operational-resilience-act (page thématique sans dates)</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -7493,7 +7509,12 @@
       </c>
       <c r="S41" s="131" t="inlineStr">
         <is>
-          <t>Actualités vérifiées (dernière le 18/09/2026) + « What's new » + consultations ouvertes. Flux RSS : actualités, consultations publiques, lignes directrices réglementaires (listés sur la page RSS d'EMA). (recherche du 23/09/2026)</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (médicaments, volume élevé). | Actualités vérifiées (dernière le 18/09/2026) + « What's new » + consultations ouvertes. Flux RSS : actualités, consultations publiques, lignes directrices réglementaires (listés sur la page RSS d'EMA). (recherche du 23/09/2026)</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7573,12 @@
       </c>
       <c r="S42" s="131" t="inlineStr">
         <is>
-          <t>Actualités + communiqués + consultations ; flux RSS repéré. (recherche du 23/09/2026)</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (télécoms, volume élevé). | Actualités + communiqués + consultations ; flux RSS repéré. (recherche du 23/09/2026)</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -7578,7 +7604,11 @@
           <t>https://health.ec.europa.eu/</t>
         </is>
       </c>
-      <c r="F43" s="129" t="n"/>
+      <c r="F43" s="129" t="inlineStr">
+        <is>
+          <t>https://health.ec.europa.eu/node/2/rss_en</t>
+        </is>
+      </c>
       <c r="G43" s="130" t="n"/>
       <c r="H43" s="147" t="inlineStr">
         <is>
@@ -7625,7 +7655,12 @@
       </c>
       <c r="S43" s="131" t="inlineStr">
         <is>
-          <t>Page « Latest updates » datée vérifiée (dernière le 18/09/2026).</t>
+          <t>v4 (28/09/2026) : flux RSS DG SANTE remis sur sa ligne ; filtrage « pertinence » (beaucoup de santé publique hors cyber). | Page « Latest updates » datée vérifiée (dernière le 18/09/2026).</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -7953,7 +7988,12 @@
       </c>
       <c r="S49" s="131" t="inlineStr">
         <is>
-          <t>Flux RSS + rubriques Legal et Government (plus proches de la réglementation que le flux général). (recherche du 23/09/2026)</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (presse cyber internationale, volume élevé). | Flux RSS + rubriques Legal et Government (plus proches de la réglementation que le flux général). (recherche du 23/09/2026)</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -8857,7 +8897,12 @@
       </c>
       <c r="S64" s="131" t="inlineStr">
         <is>
-          <t>Page actualités datée vérifiée (22/09/2026) et article ouvert avec succès. Flux RSS du site non à jour (août 2026) : non utilisé.</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (presse cyber, volume élevé). | Page actualités datée vérifiée (22/09/2026) et article ouvert avec succès. Flux RSS du site non à jour (août 2026) : non utilisé.</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -9122,9 +9167,14 @@
       </c>
       <c r="S68" s="131" t="inlineStr">
         <is>
-          <t>Dossiers législatifs (vérifiés, dépôts du 21/09/2026) + projets de loi + textes adoptés. Flux : communiqués + documents parlementaires (projets, rapports, textes). (recherche du 23/09/2026)
+          <t>v4 (28/09/2026) : filtrage « pertinence » (toutes les propositions de loi, volume élevé). | Dossiers législatifs (vérifiés, dépôts du 21/09/2026) + projets de loi + textes adoptés. Flux : communiqués + documents parlementaires (projets, rapports, textes). (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.assemblee-nationale.fr/rss/communiques-de-presse.xml (non vérifiable (serveur m'a limité, erreur 429))</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9761,12 @@
       <c r="R76" s="131" t="n"/>
       <c r="S76" s="131" t="inlineStr">
         <is>
-          <t>Flux RSS vérifié (22/09/2026) et article ouvert avec succès.</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (presse cyber, volume élevé). | Flux RSS vérifié (22/09/2026) et article ouvert avec succès.</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9839,12 @@
       <c r="R77" s="131" t="n"/>
       <c r="S77" s="131" t="inlineStr">
         <is>
-          <t>Flux RSS vérifié (23/09/2026) et article ouvert avec succès. La page rubrique affiche des dates sans année : non utilisée.</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (presse tech généraliste, volume élevé). | Flux RSS vérifié (23/09/2026) et article ouvert avec succès. La page rubrique affiche des dates sans année : non utilisée.</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11187,12 @@
       <c r="R101" s="131" t="n"/>
       <c r="S101" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 24/09/2026 : axe D — flux RSS lu le 24/09/2026 : dernier élément du 22/09/2026 ; article ouvert : https://www.redseguridad.com/actualidad/ley-europea-eu-kids-limita-acceso-ninos-redes-sociales_20260921.html (21/09/2026). Couvre régulièrement ENS/NIS2 et réglementation UE</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (presse cyber, volume élevé). | Vérif. 24/09/2026 : axe D — flux RSS lu le 24/09/2026 : dernier élément du 22/09/2026 ; article ouvert : https://www.redseguridad.com/actualidad/ley-europea-eu-kids-limita-acceso-ninos-redes-sociales_20260921.html (21/09/2026). Couvre régulièrement ENS/NIS2 et réglementation UE</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -11286,7 +11351,12 @@
       <c r="R104" s="131" t="n"/>
       <c r="S104" s="131" t="inlineStr">
         <is>
-          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (presse IT généraliste, volume élevé). | À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11515,12 @@
       <c r="R107" s="131" t="n"/>
       <c r="S107" s="131" t="inlineStr">
         <is>
-          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+          <t>v4 (28/09/2026) : filtrage « pertinence » (actualités NHS générales, volume élevé). | À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>
@@ -11482,7 +11557,7 @@
       <c r="J108" s="156" t="n"/>
       <c r="K108" s="27" t="inlineStr">
         <is>
-          <t>Actif - à confirmer</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L108" s="157" t="n"/>
@@ -11498,7 +11573,7 @@
       <c r="R108" s="131" t="n"/>
       <c r="S108" s="131" t="inlineStr">
         <is>
-          <t>À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+          <t>v4 (28/09/2026) : retirée : bloque les robots (aucun article lu lors de la collecte GitHub du 25/09/2026). | À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
         </is>
       </c>
     </row>
@@ -12503,6 +12578,333 @@
       <c r="S125" s="131" t="inlineStr">
         <is>
           <t>Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 14/04/2026 ; exemple : MDR 2.0, IVDR 2.0: What the Commission is planning (15/01/2026), MDR Classification Rule 11: The classification nightmare? (21/01/2026). Cabinet de conseil (pas d'avocats). Flux RSS non confirmé ; rythme de publication lent</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CEN-CENELEC — actualités (normalisation européenne)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Organisme de normalisation officiel</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://www.cencenelec.eu/</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Normes harmonisées (CRA, IA, DM/DIV), JTC 13.</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>https://www.cencenelec.eu/news-events/news/</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>ETSI — newsroom (normalisation télécoms et cybersécurité)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Organisme de normalisation officiel</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://www.etsi.org/</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Normes CRA (EN 18031, normes verticales), EN 303 645.</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>https://www.etsi.org/newsroom/</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Allemagne</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Bundesgesetzblatt (journal officiel fédéral)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://www.recht.bund.de/</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://www.recht.bund.de/rss/feeds/rss_bgbl-1-2.xml</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Lois et règlements fédéraux (NIS2UmsuCG, KRITIS-Dachgesetz…).</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Suède</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Svensk författningssamling (journal officiel)</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://svenskforfattningssamling.se/</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Lois et ordonnances suédoises (cybersäkerhetslag…).</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>https://svenskforfattningssamling.se/</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Suisse</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Swissmedic — actualités (via flux RSS FetchRSS)</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://www.swissmedic.ch/</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://fetchrss.com/feed/X-CSwP0MWGVCaG_Z2JbPgiti.rss</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Dispositifs médicaux et DIV en Suisse (ODim, ODiv).</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Helsedirektoratet — nyheter (direction de la santé)</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://www.helsedirektoratet.no/</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Santé numérique, normes de sécurité de l'information (Normen).</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>https://www.helsedirektoratet.no/nyheter</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>pertinence</t>
         </is>
       </c>
     </row>

--- a/config/sources.xlsx
+++ b/config/sources.xlsx
@@ -4656,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T131"/>
+  <dimension ref="A1:T175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.1796875" customWidth="1" min="1" max="1"/>
@@ -5035,14 +5035,10 @@
           <t>Accès confirmé (cert.at), rubrique meldungen/aktuelles datée (08/09/2026).</t>
         </is>
       </c>
-      <c r="R5" s="140" t="inlineStr">
-        <is>
-          <t>https://www.cert.at/de/meldungen/aktuelles</t>
-        </is>
-      </c>
+      <c r="R5" s="140" t="n"/>
       <c r="S5" s="131" t="inlineStr">
         <is>
-          <t>Flux Aktuelles + Blog ; pages Aktuelles, Spezielles, NIS2. (recherche du 23/09/2026)
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.cert.at/de/meldungen/aktuelles (illisible par le serveur GitHub). | Flux Aktuelles + Blog ; pages Aktuelles, Spezielles, NIS2. (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.cert.at/de/meldungen/spezielles (dates sans année, peu active)
 - https://www.cert.at/de/nis2 (page thématique sans dates)
@@ -5686,13 +5682,12 @@
       </c>
       <c r="R14" s="140" t="inlineStr">
         <is>
-          <t>https://www.edpb.europa.eu/news_en
-https://www.edpb.europa.eu/documents_en</t>
+          <t>https://www.edpb.europa.eu/documents_en</t>
         </is>
       </c>
       <c r="S14" s="131" t="inlineStr">
         <is>
-          <t>Flux news vérifié + flux publications + consultations. (recherche du 23/09/2026)
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.edpb.europa.eu/news_en (illisible par le serveur GitHub). | Flux news vérifié + flux publications + consultations. (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.edpb.europa.eu/public-consultations_en (périodes de consultation, pas de date de publication)</t>
         </is>
@@ -5800,15 +5795,10 @@
           <t>Blocage temporaire de mon outil de récupération levé au nouveau test. URL affinée vers la page des communiqués de presse (articles datés confirmés).</t>
         </is>
       </c>
-      <c r="R16" s="141" t="inlineStr">
-        <is>
-          <t>https://www.consilium.europa.eu/fr/press/press-releases/
-https://www.consilium.europa.eu/fr/policies/cybersecurity/</t>
-        </is>
-      </c>
+      <c r="R16" s="141" t="n"/>
       <c r="S16" s="131" t="inlineStr">
         <is>
-          <t>Flux communiqués vérifié + page politique « cybersécurité » vérifiée. (recherche du 23/09/2026)</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.consilium.europa.eu/fr/policies/cybersecurity/, https://www.consilium.europa.eu/fr/press/press-releases/ (illisible par le serveur GitHub). | Flux communiqués vérifié + page politique « cybersécurité » vérifiée. (recherche du 23/09/2026)</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5827,7 @@
       <c r="J17" s="7" t="n"/>
       <c r="K17" s="17" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L17" s="17" t="n"/>
@@ -5861,7 +5851,7 @@
       </c>
       <c r="S17" s="131" t="inlineStr">
         <is>
-          <t>Actualités + Legislative Train (suivi des textes). Flux RSS existants mais page RSS bloquée pour mon outil. (recherche du 23/09/2026)
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | Actualités + Legislative Train (suivi des textes). Flux RSS existants mais page RSS bloquée pour mon outil. (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.europarl.europa.eu/legislative-train (tableau de bord sans dates)</t>
         </is>
@@ -7503,13 +7493,12 @@
       <c r="R41" s="140" t="inlineStr">
         <is>
           <t>https://www.ema.europa.eu/en/news
-https://www.ema.europa.eu/en/news-events/whats-new
-https://www.ema.europa.eu/en/news-events/open-consultations</t>
+https://www.ema.europa.eu/en/news-events/whats-new</t>
         </is>
       </c>
       <c r="S41" s="131" t="inlineStr">
         <is>
-          <t>v4 (28/09/2026) : filtrage « pertinence » (médicaments, volume élevé). | Actualités vérifiées (dernière le 18/09/2026) + « What's new » + consultations ouvertes. Flux RSS : actualités, consultations publiques, lignes directrices réglementaires (listés sur la page RSS d'EMA). (recherche du 23/09/2026)</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.ema.europa.eu/en/news-events/open-consultations (illisible par le serveur GitHub). | v4 (28/09/2026) : filtrage « pertinence » (médicaments, volume élevé). | Actualités vérifiées (dernière le 18/09/2026) + « What's new » + consultations ouvertes. Flux RSS : actualités, consultations publiques, lignes directrices réglementaires (listés sur la page RSS d'EMA). (recherche du 23/09/2026)</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -7763,13 +7752,12 @@
       </c>
       <c r="R45" s="140" t="inlineStr">
         <is>
-          <t>https://www.anfr.fr/liste-actualites
-https://www.anfr.fr/presse-anfr</t>
+          <t>https://www.anfr.fr/presse-anfr</t>
         </is>
       </c>
       <c r="S45" s="131" t="inlineStr">
         <is>
-          <t>Actualités + espace presse. (recherche du 23/09/2026)</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.anfr.fr/liste-actualites (illisible par le serveur GitHub). | Actualités + espace presse. (recherche du 23/09/2026)</t>
         </is>
       </c>
     </row>
@@ -7868,14 +7856,10 @@
           <t>Accès confirmé, articles datés (ex. 05/09/2026).</t>
         </is>
       </c>
-      <c r="R47" s="141" t="inlineStr">
-        <is>
-          <t>https://cert.pl/</t>
-        </is>
-      </c>
+      <c r="R47" s="141" t="n"/>
       <c r="S47" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 23/09/2026 (RSS 2.0 ; beaucoup d'avis CVE mais aussi des analyses et des rapports de sujets) ; article ouvert : https://cert.pl/en/posts/2026/09/tollfraud-analysis/</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://cert.pl/ (illisible par le serveur GitHub). | Vérif. 24/09/2026 : flux lu le 24/09/2026 : dernier élément du 23/09/2026 (RSS 2.0 ; beaucoup d'avis CVE mais aussi des analyses et des rapports de sujets) ; article ouvert : https://cert.pl/en/posts/2026/09/tollfraud-analysis/</t>
         </is>
       </c>
     </row>
@@ -8146,7 +8130,7 @@
       </c>
       <c r="K52" s="148" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L52" s="148" t="inlineStr">
@@ -8178,7 +8162,7 @@
       </c>
       <c r="S52" s="131" t="inlineStr">
         <is>
-          <t>Flux RSS vérifié (dernier communiqué le 22/09/2026), article ouvert avec succès ; page d'accueil datée.</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Flux RSS vérifié (dernier communiqué le 22/09/2026), article ouvert avec succès ; page d'accueil datée.</t>
         </is>
       </c>
     </row>
@@ -8284,13 +8268,12 @@
       <c r="R54" s="140" t="inlineStr">
         <is>
           <t>https://www.aepd.es/prensa-y-comunicacion/notas-de-prensa
-https://www.aepd.es/prensa-y-comunicacion/blog
-https://www.aepd.es/informes-y-resoluciones/criterios-juridicos-aepd</t>
+https://www.aepd.es/prensa-y-comunicacion/blog</t>
         </is>
       </c>
       <c r="S54" s="131" t="inlineStr">
         <is>
-          <t>Communiqués + blog + critères juridiques (pages repérées sur le site). (recherche du 23/09/2026)</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.aepd.es/informes-y-resoluciones/criterios-juridicos-aepd (illisible par le serveur GitHub). | Communiqués + blog + critères juridiques (pages repérées sur le site). (recherche du 23/09/2026)</t>
         </is>
       </c>
     </row>
@@ -8514,13 +8497,12 @@
       <c r="R58" s="141" t="inlineStr">
         <is>
           <t>https://nki.gov.hu/it-biztonsag/hirek/
-https://nki.gov.hu/figyelmeztetesek/tajekoztatas/
-https://nki.gov.hu/it-biztonsag/kiadvanyok/</t>
+https://nki.gov.hu/figyelmeztetesek/tajekoztatas/</t>
         </is>
       </c>
       <c r="S58" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 24/09/2026 : flux hirek lu le 24/09/2026 : dernier élément du 04/09/2026 (RSS 2.0 ; le flux est en retard, le site affiche des actualités au 24/09/2026) ; article ouvert : https://nki.gov.hu/it-biztonsag/hirek/153-millio-jogositvany-adatai-szivarogtak-ki/. Flux kiadvanyok (publications) listé sur https://nki.gov.hu/intezet/tartalom/rss-csatornak/ mais non ouvert. Ne pas prendre /feed/serulekenysegek ni /feed/riasztasok (alertes).</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://nki.gov.hu/it-biztonsag/kiadvanyok/ (illisible par le serveur GitHub). | Vérif. 24/09/2026 : flux hirek lu le 24/09/2026 : dernier élément du 04/09/2026 (RSS 2.0 ; le flux est en retard, le site affiche des actualités au 24/09/2026) ; article ouvert : https://nki.gov.hu/it-biztonsag/hirek/153-millio-jogositvany-adatai-szivarogtak-ki/. Flux kiadvanyok (publications) listé sur https://nki.gov.hu/intezet/tartalom/rss-csatornak/ mais non ouvert. Ne pas prendre /feed/serulekenysegek ni /feed/riasztasok (alertes).</t>
         </is>
       </c>
     </row>
@@ -8572,13 +8554,12 @@
       </c>
       <c r="R59" s="141" t="inlineStr">
         <is>
-          <t>https://www.garanteprivacy.it/comunicati-stampa
-https://www.garanteprivacy.it/home/stampa-comunicazione/newsletter</t>
+          <t>https://www.garanteprivacy.it/comunicati-stampa</t>
         </is>
       </c>
       <c r="S59" s="131" t="inlineStr">
         <is>
-          <t>Communiqués + newsletter + thème IA ; flux RSS news repéré sur le site. (recherche du 23/09/2026)
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.garanteprivacy.it/home/stampa-comunicazione/newsletter (illisible par le serveur GitHub). | Communiqués + newsletter + thème IA ; flux RSS news repéré sur le site. (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.garanteprivacy.it/temi/intelligenza-artificiale (page thématique sans dates)</t>
         </is>
@@ -8621,7 +8602,7 @@
       </c>
       <c r="K60" s="148" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L60" s="148" t="inlineStr">
@@ -8653,7 +8634,7 @@
       </c>
       <c r="S60" s="131" t="inlineStr">
         <is>
-          <t>Page du ministère avec actualités datées vérifiée (dernière le 28/08/2026) et article ouvert avec succès.</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Page du ministère avec actualités datées vérifiée (dernière le 28/08/2026) et article ouvert avec succès.</t>
         </is>
       </c>
     </row>
@@ -8816,15 +8797,10 @@
           <t>Accès confirmé, rubrique news-and-communications datée (24/08/2026).</t>
         </is>
       </c>
-      <c r="R63" s="141" t="inlineStr">
-        <is>
-          <t>https://www.gov.uk/search/news-and-communications?organisations[]=department-for-science-innovation-and-technology
-https://www.gov.uk/search/policy-papers-and-consultations?organisations[]=department-for-science-innovation-and-technology</t>
-        </is>
-      </c>
+      <c r="R63" s="141" t="n"/>
       <c r="S63" s="131" t="inlineStr">
         <is>
-          <t>Actualités + textes et consultations (DSIT) ; flux Atom GOV.UK vérifié (actualités). (recherche du 23/09/2026)</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.gov.uk/search/news-and-communications?organisations[]=department-for-science-innovation-and-technology, https://www.gov.uk/search/policy-papers-and-consultations?organisations[]=department-for-science-innovation-and-technology (illisible par le serveur GitHub). | Actualités + textes et consultations (DSIT) ; flux Atom GOV.UK vérifié (actualités). (recherche du 23/09/2026)</t>
         </is>
       </c>
     </row>
@@ -9003,13 +8979,12 @@
       </c>
       <c r="R66" s="140" t="inlineStr">
         <is>
-          <t>https://www.imy.se/nyheter/
-https://www.imy.se/publikationer/</t>
+          <t>https://www.imy.se/publikationer/</t>
         </is>
       </c>
       <c r="S66" s="131" t="inlineStr">
         <is>
-          <t>Actualités + décisions de sanction + publications ; flux RSS repéré (sanction du 22/09/2026 visible). (recherche du 23/09/2026)
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.imy.se/link/fa3ee3124ab14f12aba446eb3a35f46e.aspx?epsremainingpath=rss, https://www.imy.se/nyheter/ (illisible par le serveur GitHub). | Actualités + décisions de sanction + publications ; flux RSS repéré (sanction du 22/09/2026 visible). (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.imy.se/om-oss/beslut-publikationer-och-remisser/beslut-om-sanktionsavgift/ (années seulement, pas de date précise)
 - https://www.imy.se/om-oss/aktuellt-fran-oss/rss/ (page HTML, pas un flux : remplacé par le vrai flux Nyheter)
@@ -9160,14 +9135,12 @@
       </c>
       <c r="R68" s="141" t="inlineStr">
         <is>
-          <t>https://www.assemblee-nationale.fr/dyn/17/dossiers
-https://www2.assemblee-nationale.fr/documents/liste/(type)/projets-loi
-https://www2.assemblee-nationale.fr/documents/liste/(type)/ta</t>
+          <t>https://www.assemblee-nationale.fr/dyn/17/dossiers</t>
         </is>
       </c>
       <c r="S68" s="131" t="inlineStr">
         <is>
-          <t>v4 (28/09/2026) : filtrage « pertinence » (toutes les propositions de loi, volume élevé). | Dossiers législatifs (vérifiés, dépôts du 21/09/2026) + projets de loi + textes adoptés. Flux : communiqués + documents parlementaires (projets, rapports, textes). (recherche du 23/09/2026)
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www2.assemblee-nationale.fr/documents/liste/(type)/projets-loi, https://www2.assemblee-nationale.fr/documents/liste/(type)/ta (illisible par le serveur GitHub). | v4 (28/09/2026) : filtrage « pertinence » (toutes les propositions de loi, volume élevé). | Dossiers législatifs (vérifiés, dépôts du 21/09/2026) + projets de loi + textes adoptés. Flux : communiqués + documents parlementaires (projets, rapports, textes). (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.assemblee-nationale.fr/rss/communiques-de-presse.xml (non vérifiable (serveur m'a limité, erreur 429))</t>
         </is>
@@ -9509,7 +9482,7 @@
       </c>
       <c r="K73" s="29" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L73" s="17" t="inlineStr">
@@ -9541,7 +9514,7 @@
       </c>
       <c r="S73" s="131" t="inlineStr">
         <is>
-          <t>Liste vérifiée (dernière le 22/09/2026) ; pas de filtre Bulgarie/cyber exploitable par URL. (recherche du 23/09/2026)</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | Liste vérifiée (dernière le 22/09/2026) ; pas de filtre Bulgarie/cyber exploitable par URL. (recherche du 23/09/2026)</t>
         </is>
       </c>
     </row>
@@ -10260,14 +10233,10 @@
       <c r="O84" s="159" t="n"/>
       <c r="P84" s="153" t="n"/>
       <c r="Q84" s="160" t="n"/>
-      <c r="R84" s="131" t="inlineStr">
-        <is>
-          <t>https://www.agid.gov.it/it/notizie</t>
-        </is>
-      </c>
+      <c r="R84" s="131" t="n"/>
       <c r="S84" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 24/09/2026 : axe B — flux lu le 24/09/2026 : dernier élément du 21/09/2026 ; article ouvert : https://www.agid.gov.it/it/notizie/dichiarazione-di-accessibilita-pubblicazione-o-aggiornamento-entro-il-23-settembre</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.agid.gov.it/it/notizie (illisible par le serveur GitHub). | Vérif. 24/09/2026 : axe B — flux lu le 24/09/2026 : dernier élément du 21/09/2026 ; article ouvert : https://www.agid.gov.it/it/notizie/dichiarazione-di-accessibilita-pubblicazione-o-aggiornamento-entro-il-23-settembre</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10322,7 @@
       <c r="J86" s="156" t="n"/>
       <c r="K86" s="27" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L86" s="157" t="n"/>
@@ -10373,7 +10342,7 @@
       </c>
       <c r="S86" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 24/09/2026 : axe C — page lue le 24/09/2026 (pas de flux RSS : /feed/ = 404) : dernier élément du 23/09/2026 ; article ouvert : https://z-cert.nl/actueel/nieuws/de-cyberbeveiligingswet-is-van-kracht (15/08/2026, entrée en vigueur de la Cyberbeveiligingswet / NIS2 NL). Mélange actus réglementaires et avertissements (phishing, WordPress).</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Vérif. 24/09/2026 : axe C — page lue le 24/09/2026 (pas de flux RSS : /feed/ = 404) : dernier élément du 23/09/2026 ; article ouvert : https://z-cert.nl/actueel/nieuws/de-cyberbeveiligingswet-is-van-kracht (15/08/2026, entrée en vigueur de la Cyberbeveiligingswet / NIS2 NL). Mélange actus réglementaires et avertissements (phishing, WordPress).</t>
         </is>
       </c>
     </row>
@@ -11835,7 +11804,7 @@
       <c r="J113" s="156" t="n"/>
       <c r="K113" s="27" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L113" s="157" t="n"/>
@@ -11855,7 +11824,7 @@
       </c>
       <c r="S113" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (flux /feed/ vide) : dernier élément du 23/06/2026 ; exemples : A practical path to EU-US cybersecurity mutual recognition ; AI in healthcare policy paper (08/06/2026)</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | Vérif. 25/09/2026 : page lue le 25/09/2026 (flux /feed/ vide) : dernier élément du 23/06/2026 ; exemples : A practical path to EU-US cybersecurity mutual recognition ; AI in healthcare policy paper (08/06/2026)</t>
         </is>
       </c>
     </row>
@@ -11954,7 +11923,7 @@
       <c r="J115" s="156" t="n"/>
       <c r="K115" s="27" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L115" s="157" t="n"/>
@@ -11974,7 +11943,7 @@
       </c>
       <c r="S115" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux RSS) : dernier élément du 24/09/2026 ; exemple : Europe's security moment: Time to widen the options. Généraliste, filtrer par mots-clés numérique/cyber</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux RSS) : dernier élément du 24/09/2026 ; exemple : Europe's security moment: Time to widen the options. Généraliste, filtrer par mots-clés numérique/cyber</t>
         </is>
       </c>
       <c r="T115" t="inlineStr">
@@ -12016,7 +11985,7 @@
       <c r="J116" s="156" t="n"/>
       <c r="K116" s="27" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L116" s="157" t="n"/>
@@ -12036,7 +12005,7 @@
       </c>
       <c r="S116" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 17/09/2026 ; exemple : China's artificial intelligence goals and strategic choices for Europe (10/09/2026). Ne pas utiliser rss.xml (sessions d'événements). Pertinence cyber faible, filtrer</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 17/09/2026 ; exemple : China's artificial intelligence goals and strategic choices for Europe (10/09/2026). Ne pas utiliser rss.xml (sessions d'événements). Pertinence cyber faible, filtrer</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -12197,7 +12166,7 @@
       <c r="J119" s="156" t="n"/>
       <c r="K119" s="27" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L119" s="157" t="n"/>
@@ -12217,7 +12186,7 @@
       </c>
       <c r="S119" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux) : dernier élément affiché du 29/05/2026 ; exemples : Cyber Resilience Act and Franchise Networks ; Physical AI in the Digital Omnibus – Update (27/05/2026). Liste peut-être incomplète, à surveiller</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux) : dernier élément affiché du 29/05/2026 ; exemples : Cyber Resilience Act and Franchise Networks ; Physical AI in the Digital Omnibus – Update (27/05/2026). Liste peut-être incomplète, à surveiller</t>
         </is>
       </c>
     </row>
@@ -12380,7 +12349,7 @@
       <c r="J122" s="156" t="n"/>
       <c r="K122" s="27" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L122" s="157" t="n"/>
@@ -12400,7 +12369,7 @@
       </c>
       <c r="S122" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux RSS exploitable : /feed renvoie du HTML, /news/ est un gabarit vide) : dernier élément du 10/08/2026 ; exemples : Joint position: Smarter MDR and IVDR oversight (23/06/2026), Targeted revision of EU MDR Rule 11 for medical device software (30/04/2026), Joint industry statement on the AI omnibus (12/03/2026), Safeguarding IP and trade secrets in the EHDS (15/01/2026)</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux RSS exploitable : /feed renvoie du HTML, /news/ est un gabarit vide) : dernier élément du 10/08/2026 ; exemples : Joint position: Smarter MDR and IVDR oversight (23/06/2026), Targeted revision of EU MDR Rule 11 for medical device software (30/04/2026), Joint industry statement on the AI omnibus (12/03/2026), Safeguarding IP and trade secrets in the EHDS (15/01/2026)</t>
         </is>
       </c>
     </row>
@@ -12452,13 +12421,12 @@
       <c r="Q123" s="160" t="n"/>
       <c r="R123" s="131" t="inlineStr">
         <is>
-          <t>https://www.bvmed.de/themen/regulatorik-mdr
-https://www.bvmed.de/de/bvmed/presse/pressemeldungen</t>
+          <t>https://www.bvmed.de/themen/regulatorik-mdr</t>
         </is>
       </c>
       <c r="S123" s="131" t="inlineStr">
         <is>
-          <t>Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 16/09/2026 ; exemples : Rede zur Lage der EU: KI und Gesundheit im Fokus, aber mit effizienter Regulierung (16/09/2026), KI-Verordnung: Was jetzt gilt und was der KI-Omnibus verschoben hat (30/07/2026), Stellungnahme: Medizinprodukte und In-vitro-Diagnostika – gezielte Überarbeitung der EU-Vorschriften (16/07/2026). Flux RSS existant mais URL générée par formulaire (https://www.bvmed.de/rss) : non récupérée, à générer à la main</t>
+          <t>28/09/2026 (v4.1) : retiré(s) : https://www.bvmed.de/de/bvmed/presse/pressemeldungen (illisible par le serveur GitHub). | Vérif. 25/09/2026 : page lue le 25/09/2026 : dernier élément du 16/09/2026 ; exemples : Rede zur Lage der EU: KI und Gesundheit im Fokus, aber mit effizienter Regulierung (16/09/2026), KI-Verordnung: Was jetzt gilt und was der KI-Omnibus verschoben hat (30/07/2026), Stellungnahme: Medizinprodukte und In-vitro-Diagnostika – gezielte Überarbeitung der EU-Vorschriften (16/07/2026). Flux RSS existant mais URL générée par formulaire (https://www.bvmed.de/rss) : non récupérée, à générer à la main</t>
         </is>
       </c>
     </row>
@@ -12765,7 +12733,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -12790,7 +12758,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
         </is>
       </c>
       <c r="T129" t="inlineStr">
@@ -12874,35 +12842,2457 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
+          <t>Inactif</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>v4</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Santé numérique, normes de sécurité de l'information (Normen).</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>https://www.helsedirektoratet.no/nyheter</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Nkom (régulateur des communications électroniques, sécurité numérique)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://nkom.no/</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://nkom.no/aktuelt/rss.xml</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
           <t>Actif</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr">
-        <is>
-          <t>v4</t>
-        </is>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>28/09/2026</t>
-        </is>
-      </c>
-      <c r="Q131" t="inlineStr">
-        <is>
-          <t>Santé numérique, normes de sécurité de l'information (Normen).</t>
-        </is>
-      </c>
-      <c r="R131" t="inlineStr">
-        <is>
-          <t>https://www.helsedirektoratet.no/nyheter</t>
-        </is>
-      </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>v4 (28/09/2026) : ajoutée (accès robot vérifié).</t>
-        </is>
-      </c>
-      <c r="T131" t="inlineStr">
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Sécurité ekom, loi sur la sécurité numérique.</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Digdir (agence norvégienne du numérique)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://www.digdir.no/</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Loi sur la sécurité numérique (digitalsikkerhetsloven), services publics numériques.</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>https://www.digdir.no/digdir/nyheitsarkiv/691</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Stortinget — lois votées (lovvedtak)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://www.stortinget.no/</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://www.stortinget.no/no/Stottemeny/RSS/Lovbeslutninger/</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Législation votée ; toutes matières, filtrée.</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Norvège</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Digi.no (presse numérique norvégienne)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://www.digi.no/</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://www.digi.no/?lab_viewport=rss</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Presse tech ; volumineuse, filtrée.</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Danemark</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Lægemiddelstyrelsen (médicaments et dispositifs médicaux)</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://laegemiddelstyrelsen.dk/</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://laegemiddelstyrelsen.dk/da/Feeds/rss-feed</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Dispositifs médicaux / DIV ; surtout médicaments, filtrée.</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Danemark</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Høringsportalen — consultations (numérique, justice, santé)</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://hoeringsportalen.dk/</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://hoeringsportalen.dk/syndication/HearingsByAuthorityFeed?authorityId=709
+https://hoeringsportalen.dk/syndication/HearingsByAuthorityFeed?authorityId=607
+https://hoeringsportalen.dk/syndication/HearingsByAuthorityFeed?authorityId=1725
+https://hoeringsportalen.dk/syndication/HearingsByAuthorityFeed?authorityId=1727
+https://hoeringsportalen.dk/syndication/HearingsByAuthorityFeed?authorityId=1768</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Projets de lois et d'arrêtés en consultation : Digitaliseringsstyrelsen, Justitsministeriet, Lægemiddelstyrelsen, Sundhedsdatastyrelsen, Digitaliseringsministeriet.</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Danemark</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Indenrigs- og Sundhedsministeriet (ministère de la santé)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://www.ism.dk/</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://www.ism.dk/handlers/DynamicRss.ashx?id=ef93e4ce-ba0b-43e6-8f75-edab7d4faaea</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Santé, données de santé.</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Danemark</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Version2 (presse IT danoise)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://www.version2.dk/</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://www.version2.dk/rss</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>IA, santé numérique, sécurité.</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Finlande</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Fimea (médicaments et dispositifs médicaux)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://fimea.fi/</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://fimea.fi/en/current-events/-/asset_publisher/6Fp1W0OnZUR7/rss</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Dispositifs médicaux, AI Act appliqué aux DM.</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Finlande</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Tietosuojavaltuutettu (autorité de protection des données)</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://tietosuoja.fi/</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Protection des données.</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>https://tietosuoja.fi/en/current-issues</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Finlande</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Valtioneuvosto — communiqués et projets de loi du gouvernement</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://valtioneuvosto.fi/</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://valtioneuvosto.fi/en/staattiset-feedit-en/-/asset_publisher/LOmkEPY4nk2s/rss</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Tous ministères ; projets de loi (hallituksen esitykset).</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>https://valtioneuvosto.fi/paatokset/hallituksen-esitykset</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Finlande</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>STM (ministère des affaires sociales et de la santé)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://stm.fi/</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Santé, données de santé.</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>https://stm.fi/tiedotteet-ja-uutiset</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Suède</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>PTS (autorité de supervision NIS2 / cybersäkerhetslagen)</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://pts.se/</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Loi cyber suédoise (cybersäkerhetslagen).</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>https://pts.se/nyheter-och-pressmeddelanden/</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Suède</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>IVO (inspection de la santé, supervision NIS2 secteur santé)</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://www.ivo.se/</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://via.tt.se/rss/releases/latest?publisherId=3236124</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Supervision NIS2 du secteur santé.</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Suède</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Riksdagen — projets de loi (propositions)</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://www.riksdagen.se/</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://data.riksdagen.se/dokumentlista/?avd=dokument&amp;doktyp=prop&amp;sort=datum&amp;sortorder=desc&amp;utformat=rss</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Législation (remplace Svensk författningssamling, bloquée).</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Suède</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Regeringen — consultations (remisser)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://www.regeringen.se/</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Consultations sur projets de textes.</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>https://www.regeringen.se/remisser/</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Suède</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Computer Sweden — réglementation</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://computersweden.se/</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Presse IT, rubrique réglementation.</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>https://computersweden.se/regulation/</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Belgique</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Plateforme eHealth (SPF Santé publique)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://www.ehealth.fgov.be/</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://www.ehealth.fgov.be/ehealthplatform/fr/rss/news</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Santé numérique ; contenu technique, filtré.</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Pays-Bas</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Digitale Overheid (ministère de l'Intérieur, BZK)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://www.digitaleoverheid.nl/</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://www.digitaleoverheid.nl/feed/</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>RGPD, IA, Cyberbeveiligingswet (NIS2).</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Pays-Bas</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>RDI — Rijksinspectie Digitale Infrastructuur (autorité NIS2)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://www.rdi.nl/</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Autorité de contrôle de la Cyberbeveiligingswet (en vigueur 15/08/2026).</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>https://www.rdi.nl/actueel</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Pays-Bas</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Rijksoverheid — cybercriminalité et cybersécurité</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://www.rijksoverheid.nl/</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Gouvernement : lois cyber, entités critiques.</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>https://www.rijksoverheid.nl/themas/recht-veiligheid-en-defensie/cybercrime-en-cybersecurity</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Pays-Bas</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>IGJ — technologie médicale (inspection santé)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://www.igj.nl/</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Dispositifs médicaux, sécurité de l'information des laboratoires.</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>https://www.igj.nl/zorgsectoren/medische-technologie</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Pays-Bas</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ICTRecht — blog</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Cabinet d'avocats</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.ictrecht.nl/</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Droit du numérique néerlandais.</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>https://www.ictrecht.nl/blog</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Autriche</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>DSB (Datenschutzbehörde)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://dsb.gv.at/</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Protection des données.</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>https://dsb.gv.at/aktuelles/</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Autriche</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>BASG — sécurité des dispositifs médicaux</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://basg.gv.at/</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Dispositifs médicaux et DIV.</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>https://basg.gv.at/medizinprodukte/amtliche-nachrichten/sicherheitsinformationen</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Autriche</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>RTR — KI-Servicestelle (IA)</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://www.rtr.at/</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>AI Act en Autriche.</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>https://www.rtr.at/rtr/service/ki-servicestelle/ki-servicestelle.de.html</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Autriche</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>USP — NIS-2 (portail entreprises)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://www.usp.gv.at/</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>NISG 2026 (en vigueur 01/10/2026), enregistrement NIS2.</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>https://www.usp.gv.at/aktuelles/newsliste/NIS-2.html</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Suisse</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Netzwoche (presse IT suisse)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://www.netzwoche.ch/</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://www.netzwoche.ch/taxonomy/term/31/feed</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Presse IT ; filtrée.</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Suisse</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>admin.ch — communiqués du Conseil fédéral et de l'administration</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://www.admin.ch/</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Gouvernement fédéral (loi sur la cybersécurité, nLPD) ; volumineux, filtré.</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>https://www.admin.ch/de/newnsb</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Suisse</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Swissmedic — dispositifs médicaux (page directe)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://www.swissmedic.ch/swissmedic/en/home/medical-devices.html</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Dispositifs médicaux, DIV (ODiv, swissdamed).</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>https://www.swissmedic.ch/swissmedic/en/home/medical-devices/overview-medical-devices.html</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Suisse</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>datenrecht.ch (Walder Wyss)</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Cabinet d'avocats</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://datenrecht.ch/</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>Droit suisse des données, motions parlementaires.</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>https://datenrecht.ch/en/updates/</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Rép. Tchèque</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SÚKL (médicaments et dispositifs médicaux)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://sukl.gov.cz/</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://sukl.gov.cz/feed/</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>Dispositifs médicaux ; flux global filtré.</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Rép. Tchèque</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Vláda ČR — centre de presse du gouvernement</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://vlada.gov.cz/</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>Gouvernement ; filtré.</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>https://vlada.gov.cz/cz/media-centrum/</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Rép. Tchèque</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Lupa.cz — actualités</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.lupa.cz/</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://www.lupa.cz/rss/aktuality/</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>Presse numérique tchèque.</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Hongrie</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>NAIH (autorité de protection des données)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://www.naih.hu/</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>Protection des données.</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>https://www.naih.hu/hirek</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Hongrie</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>HWSW (presse IT hongroise)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>https://www.hwsw.hu/</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>Presse IT.</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>https://www.hwsw.hu/</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Federprivacy</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.federprivacy.org/</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://www.federprivacy.org/strumenti/feed/tutte-le-notizie-dal-sito-di-federprivacy</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>Protection des données, IA.</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Dipartimento per la trasformazione digitale</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://innovazione.gov.it/</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>Numérique public, IA.</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>https://innovazione.gov.it/notizie/</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Italie</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>AGENAS (agence nationale des services de santé régionaux)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://www.agenas.gov.it/</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>Santé numérique.</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>https://www.agenas.gov.it/aree-tematiche/comunicazione/comunicati-stampa</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Assembleia da República — dernières initiatives</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.parlamento.pt/</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>Projets et propositions de loi.</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>https://www.parlamento.pt/Paginas/UltimasIniciativasEntradas.aspx</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>HealthNews.pt</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://healthnews.pt/</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://healthnews.pt/feed/</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Presse santé ; flux à confirmer en collecte.</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>https://healthnews.pt/</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Grèce</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>EOF — dispositifs médicaux</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://www.eof.gr/</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.eof.gr/category/iatrotexnologika/feed/</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Dispositifs médicaux / DIV (rappels, textes).</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>https://www.eof.gr/category/iatrotexnologika/</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Grèce</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Parlement grec — projets de loi déposés</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Site gouvernemental officiel</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://www.hellenicparliament.gr/</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.hellenicparliament.gr/rssfeed/RssSubmittedBills.aspx</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Projets de loi.</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Grèce</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Lawspot — législation</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Presse spécialisée</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://www.lawspot.gr/</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>v4.2</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>29/09/2026</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Actualité législative et consultations.</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>https://www.lawspot.gr/katigories-eidiseon/nomothesia/</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
         <is>
           <t>pertinence</t>
         </is>

--- a/config/sources.xlsx
+++ b/config/sources.xlsx
@@ -15212,7 +15212,7 @@
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>Actif</t>
+          <t>Inactif</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
@@ -15232,7 +15232,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
+          <t>30/09/2026 : retirée, le site refuse le serveur GitHub (403). | v4.2 (29/09/2026) : vérifiée par lecture web (flux ou page datée, élément récent) ; accès robot à confirmer à la collecte GitHub.</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -15330,46 +15330,45 @@
   </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" display="CERT-EU" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" display="CERT-EU" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId38"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId37"/>
   </tableParts>
 </worksheet>
 </file>

--- a/config/sources.xlsx
+++ b/config/sources.xlsx
@@ -4656,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T175"/>
+  <dimension ref="A1:U175"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.1796875" customWidth="1" min="1" max="1"/>
@@ -4782,6 +4782,11 @@
           <t>Filtrage (vide = tout garder ; « pertinence » = source très volumineuse, ne garder que pertinence moyenne ou élevée)</t>
         </is>
       </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Motif de retrait (si Inactif) : robots / javascript / doublon / remplacee, puis la date</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="29" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
@@ -5114,6 +5119,11 @@
           <t>Vérif. 24/09/2026 : flux RSS lu (16/09/2026, CRA et NIS2) ; articles 403 pour un robot, lisibles dans un navigateur</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>robots 24/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="16" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -5258,6 +5268,11 @@
       <c r="S8" s="131" t="inlineStr">
         <is>
           <t>v4 (28/09/2026) : retirée : bloque les robots (aucun article lu lors de la collecte GitHub du 25/09/2026). | À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -5854,6 +5869,11 @@
           <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | Actualités + Legislative Train (suivi des textes). Flux RSS existants mais page RSS bloquée pour mon outil. (recherche du 23/09/2026)
 Retiré le 23/09/2026 :
 - https://www.europarl.europa.eu/legislative-train (tableau de bord sans dates)</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>javascript 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -7809,6 +7829,11 @@
           <t>Doublon de « Agence pour la sécurité sociétale » : passé en Inactif.</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>doublon Agence pour la sécurité sociétale (samsik.dk)</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
@@ -8165,6 +8190,11 @@
           <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Flux RSS vérifié (dernier communiqué le 22/09/2026), article ouvert avec succès ; page d'accueil datée.</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="16" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
@@ -8637,6 +8667,11 @@
           <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Page du ministère avec actualités datées vérifiée (dernière le 28/08/2026) et article ouvert avec succès.</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
@@ -8930,6 +8965,11 @@
           <t>Doublon de « Agence pour la défense civile » : passé en Inactif.</t>
         </is>
       </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>doublon Agence pour la défense civile (mcf.se)</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="97" t="inlineStr">
@@ -9515,6 +9555,11 @@
       <c r="S73" s="131" t="inlineStr">
         <is>
           <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | Liste vérifiée (dernière le 22/09/2026) ; pas de filtre Bulgarie/cyber exploitable par URL. (recherche du 23/09/2026)</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>javascript 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -10345,6 +10390,11 @@
           <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Vérif. 24/09/2026 : axe C — page lue le 24/09/2026 (pas de flux RSS : /feed/ = 404) : dernier élément du 23/09/2026 ; article ouvert : https://z-cert.nl/actueel/nieuws/de-cyberbeveiligingswet-is-van-kracht (15/08/2026, entrée en vigueur de la Cyberbeveiligingswet / NIS2 NL). Mélange actus réglementaires et avertissements (phishing, WordPress).</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="152" t="inlineStr">
@@ -11545,6 +11595,11 @@
           <t>v4 (28/09/2026) : retirée : bloque les robots (aucun article lu lors de la collecte GitHub du 25/09/2026). | À tester en conditions réelles : bloqué (403/anti-robot) pour mon outil le 24/09/2026, le serveur GitHub peut y avoir accès. Voir l’onglet Sources du site après la collecte.</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="152" t="inlineStr">
@@ -11827,6 +11882,11 @@
           <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | Vérif. 25/09/2026 : page lue le 25/09/2026 (flux /feed/ vide) : dernier élément du 23/06/2026 ; exemples : A practical path to EU-US cybersecurity mutual recognition ; AI in healthcare policy paper (08/06/2026)</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>javascript 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="152" t="inlineStr">
@@ -11951,6 +12011,11 @@
           <t>pertinence</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="152" t="inlineStr">
@@ -12011,6 +12076,11 @@
       <c r="T116" t="inlineStr">
         <is>
           <t>pertinence</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -12189,6 +12259,11 @@
           <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (403 / blocage des robots). | Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux) : dernier élément affiché du 29/05/2026 ; exemples : Cyber Resilience Act and Franchise Networks ; Physical AI in the Digital Omnibus – Update (27/05/2026). Liste peut-être incomplète, à surveiller</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="152" t="inlineStr">
@@ -12372,6 +12447,11 @@
           <t>28/09/2026 (v4.1) : retirée : illisible par le serveur GitHub (page chargée en JavaScript, aucun article). | Vérif. 25/09/2026 : page lue le 25/09/2026 (pas de flux RSS exploitable : /feed renvoie du HTML, /news/ est un gabarit vide) : dernier élément du 10/08/2026 ; exemples : Joint position: Smarter MDR and IVDR oversight (23/06/2026), Targeted revision of EU MDR Rule 11 for medical device software (30/04/2026), Joint industry statement on the AI omnibus (12/03/2026), Safeguarding IP and trade secrets in the EHDS (15/01/2026)</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>javascript 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="152" t="inlineStr">
@@ -12766,6 +12846,11 @@
           <t>pertinence</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>robots 28/09/2026</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -12873,6 +12958,11 @@
       <c r="T131" t="inlineStr">
         <is>
           <t>pertinence</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>javascript 28/09/2026</t>
         </is>
       </c>
     </row>
@@ -15238,6 +15328,11 @@
       <c r="T174" t="inlineStr">
         <is>
           <t>pertinence</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>robots 30/09/2026</t>
         </is>
       </c>
     </row>

--- a/config/sources.xlsx
+++ b/config/sources.xlsx
@@ -4656,7 +4656,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U175"/>
+  <dimension ref="A1:U178"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.1796875" customWidth="1" min="1" max="1"/>
@@ -15390,6 +15390,153 @@
       <c r="T175" t="inlineStr">
         <is>
           <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Worldwide</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Inside Privacy (blog Covington &amp; Burling – données et cybersécurité)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://www.insideprivacy.com/</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://www.insideprivacy.com/feed</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>cabinet</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Ajout 30/10/2026 : flux RSS annoncé sur les articles, contenu lisible sans compte ; ex. amendements NIS2 proposés (23/01/2026). Contenu en partie US : garder seulement pertinence moyenne ou élevée.</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>pertinence</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Orgalim (industries technologiques européennes) – positions</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://orgalim.eu/</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>https://orgalim.eu/en/resources/
+https://orgalim.eu/news/</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Ajout 30/10/2026 : pas de flux RSS trouvé ; pages Resources et News ; positions CRA, Cybersecurity Act 2 (fabricants de produits connectés). Accès robot à confirmer à la collecte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Europe</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>ECSO (European Cyber Security Organisation) – analyses</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Avis d'experts (non certifié)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://ecs-org.eu/</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>30/10/2026</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>https://ecs-org.eu/news/ecso_publications/policy-analysis</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Ajout 30/10/2026 : pas de flux RSS ; page « policy analysis » lisible en HTML (révision Cybersecurity Act, amendements NIS2) ; protection anti-robots possible : à confirmer à la collecte.</t>
         </is>
       </c>
     </row>
